--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/eau/RANDOMSEARCH_DETAILS_eau.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/eau/RANDOMSEARCH_DETAILS_eau.xlsx
@@ -413,9 +413,5006 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Compose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID_Pretraitement</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code_R_Pretraitement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Meilleurs_Hyperparam_RF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RMSEC</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RMSECV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(1,3,5))</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.1723</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.8032</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9857</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.0685</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.6412</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.9488</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.8195</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,700,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9712</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.8848</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.8581</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,750,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9578</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.393</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.9352</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1000,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9717</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.8433</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.4422</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.7956</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.4061</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1200,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9835</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.6258</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9728</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.7799</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7.427</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9618</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.2396</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7.4257</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9728</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.7861</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7.4512</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9724</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.792</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7.4513</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9728</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.7905</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.4331</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9725</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.7905</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.4406</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9724</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.7983</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7.4343</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.7657</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7.4179</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.4646</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6.5941</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.7406</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.6163</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9714</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.7103</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6.7229</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9684</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.8653</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.8132</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9747</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.6108</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6.8931</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.6976</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6.9435</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9648</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.0088</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7.0814</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9611</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.1526</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7.1203</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9758</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.5894</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6.611</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.6873</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6.5785</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9758</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.6004</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6.5423</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.6156</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6.5838</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9722</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.7233</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6.6851</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9752</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.5863</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6.7375</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9661</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.9307</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6.8819</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9736</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.6523</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6.923</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.8199</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6.8102</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9629</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.2711</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6.7429</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.4375</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6.6389</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.4229</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6.7388</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.7033</v>
+      </c>
+      <c r="G38" t="n">
+        <v>6.6555</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.4231</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6.7567</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9775</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.703</v>
+      </c>
+      <c r="G40" t="n">
+        <v>6.7916</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9644</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.2334</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.8171</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9627</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.2728</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6.7383</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9813</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.5948</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6.6395</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.3958</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.7537</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9768</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.7082</v>
+      </c>
+      <c r="G45" t="n">
+        <v>6.6776</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.6999</v>
+      </c>
+      <c r="G46" t="n">
+        <v>6.7973</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9781</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.6879</v>
+      </c>
+      <c r="G47" t="n">
+        <v>6.7913</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1400,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9862</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2.4051</v>
+      </c>
+      <c r="G48" t="n">
+        <v>6.6567</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(40,1300,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2.5386</v>
+      </c>
+      <c r="G49" t="n">
+        <v>6.5669</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9841</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.0631</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5.5792</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9747</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.9004</v>
+      </c>
+      <c r="G51" t="n">
+        <v>7.1222</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.928</v>
+      </c>
+      <c r="G52" t="n">
+        <v>7.26</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.4269</v>
+      </c>
+      <c r="G53" t="n">
+        <v>6.8156</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9756</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.7161</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6.955</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2.1524</v>
+      </c>
+      <c r="G55" t="n">
+        <v>6.0202</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.2143</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5.739</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,650,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9842</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.1137</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5.4916</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,15))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.9582000000000001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.3829</v>
+      </c>
+      <c r="G58" t="n">
+        <v>7.9759</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,21))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.9589</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.3735</v>
+      </c>
+      <c r="G59" t="n">
+        <v>7.9709</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,25))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.3885</v>
+      </c>
+      <c r="G60" t="n">
+        <v>7.9761</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.9566</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.412</v>
+      </c>
+      <c r="G61" t="n">
+        <v>8.0192</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.9792</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2.4255</v>
+      </c>
+      <c r="G62" t="n">
+        <v>6.0189</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.4553</v>
+      </c>
+      <c r="G63" t="n">
+        <v>6.0868</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9772</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.5117</v>
+      </c>
+      <c r="G64" t="n">
+        <v>6.1346</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2.2955</v>
+      </c>
+      <c r="G65" t="n">
+        <v>6.1676</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9853</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.9944</v>
+      </c>
+      <c r="G66" t="n">
+        <v>5.4229</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,700,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.9833</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.1416</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5.5704</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2.156</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5.5785</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>72</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9726</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.7223</v>
+      </c>
+      <c r="G69" t="n">
+        <v>6.539</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>73</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9671999999999999</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.8527</v>
+      </c>
+      <c r="G70" t="n">
+        <v>6.5651</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>74</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9748</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2.6176</v>
+      </c>
+      <c r="G71" t="n">
+        <v>6.3804</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>75</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.9738</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2.6509</v>
+      </c>
+      <c r="G72" t="n">
+        <v>6.4414</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>76</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9784</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.9238</v>
+      </c>
+      <c r="G73" t="n">
+        <v>7.2592</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.9899</v>
+      </c>
+      <c r="G74" t="n">
+        <v>7.5148</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>78</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.9491000000000001</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.6706</v>
+      </c>
+      <c r="G75" t="n">
+        <v>7.6149</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>79</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.9491000000000001</v>
+      </c>
+      <c r="F76" t="n">
+        <v>3.6706</v>
+      </c>
+      <c r="G76" t="n">
+        <v>7.6149</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>80</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.9703000000000001</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.9525</v>
+      </c>
+      <c r="G77" t="n">
+        <v>8.0817</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>81</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.9621</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3.2336</v>
+      </c>
+      <c r="G78" t="n">
+        <v>8.068899999999999</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>82</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.9611</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3.3536</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8.0502</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>83</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2.9679</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8.074999999999999</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>84</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2.1298</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5.7675</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>85</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2.1805</v>
+      </c>
+      <c r="G82" t="n">
+        <v>5.8321</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>86</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9681999999999999</v>
+      </c>
+      <c r="F83" t="n">
+        <v>3.0943</v>
+      </c>
+      <c r="G83" t="n">
+        <v>7.5546</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>87</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9482</v>
+      </c>
+      <c r="F84" t="n">
+        <v>3.6807</v>
+      </c>
+      <c r="G84" t="n">
+        <v>7.5922</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>88</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.9678</v>
+      </c>
+      <c r="F85" t="n">
+        <v>3.092</v>
+      </c>
+      <c r="G85" t="n">
+        <v>7.5748</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>89</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9761</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2.6047</v>
+      </c>
+      <c r="G86" t="n">
+        <v>6.6044</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>90</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2.5908</v>
+      </c>
+      <c r="G87" t="n">
+        <v>6.5708</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>91</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.9737</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2.6315</v>
+      </c>
+      <c r="G88" t="n">
+        <v>6.5228</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>92</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.9748</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2.6146</v>
+      </c>
+      <c r="G89" t="n">
+        <v>6.6326</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>93</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2.5971</v>
+      </c>
+      <c r="G90" t="n">
+        <v>6.6414</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>94</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2.3984</v>
+      </c>
+      <c r="G91" t="n">
+        <v>6.7543</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>95</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9737</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2.6315</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6.5228</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>96</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2.3984</v>
+      </c>
+      <c r="G93" t="n">
+        <v>6.7543</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>97</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="F94" t="n">
+        <v>3.9488</v>
+      </c>
+      <c r="G94" t="n">
+        <v>6.8195</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>98</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.9407</v>
+      </c>
+      <c r="F95" t="n">
+        <v>3.5304</v>
+      </c>
+      <c r="G95" t="n">
+        <v>7.041</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>99</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.9214</v>
+      </c>
+      <c r="F96" t="n">
+        <v>3.9606</v>
+      </c>
+      <c r="G96" t="n">
+        <v>6.8107</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9209000000000001</v>
+      </c>
+      <c r="F97" t="n">
+        <v>3.972</v>
+      </c>
+      <c r="G97" t="n">
+        <v>6.816</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>101</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2.6991</v>
+      </c>
+      <c r="G98" t="n">
+        <v>6.5046</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>102</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9776</v>
+      </c>
+      <c r="F99" t="n">
+        <v>2.6033</v>
+      </c>
+      <c r="G99" t="n">
+        <v>6.571</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>103</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.9746</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2.7024</v>
+      </c>
+      <c r="G100" t="n">
+        <v>6.6596</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>104</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2.3796</v>
+      </c>
+      <c r="G101" t="n">
+        <v>6.7068</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>105</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.9752999999999999</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2.628</v>
+      </c>
+      <c r="G102" t="n">
+        <v>6.7076</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>106</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="F103" t="n">
+        <v>2.733</v>
+      </c>
+      <c r="G103" t="n">
+        <v>6.8517</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2.6357</v>
+      </c>
+      <c r="G104" t="n">
+        <v>6.5076</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>108</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.9766</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2.6562</v>
+      </c>
+      <c r="G105" t="n">
+        <v>6.5572</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>109</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9776</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2.5694</v>
+      </c>
+      <c r="G106" t="n">
+        <v>6.5608</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>110</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9724</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2.7994</v>
+      </c>
+      <c r="G107" t="n">
+        <v>6.6836</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>111</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9796</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2.7218</v>
+      </c>
+      <c r="G108" t="n">
+        <v>7.1614</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>112</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9806</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2.6966</v>
+      </c>
+      <c r="G109" t="n">
+        <v>6.8116</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>113</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9805</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2.5965</v>
+      </c>
+      <c r="G110" t="n">
+        <v>6.5024</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>114</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.9768</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2.6509</v>
+      </c>
+      <c r="G111" t="n">
+        <v>6.4606</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>115</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9795</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2.8263</v>
+      </c>
+      <c r="G112" t="n">
+        <v>7.1571</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>116</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9621</v>
+      </c>
+      <c r="F113" t="n">
+        <v>3.3734</v>
+      </c>
+      <c r="G113" t="n">
+        <v>6.8124</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>117</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2.6002</v>
+      </c>
+      <c r="G114" t="n">
+        <v>6.5395</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>118</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.9733000000000001</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2.7357</v>
+      </c>
+      <c r="G115" t="n">
+        <v>6.4034</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>119</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.9697</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2.666</v>
+      </c>
+      <c r="G116" t="n">
+        <v>6.1272</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>120</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2.5903</v>
+      </c>
+      <c r="G117" t="n">
+        <v>6.1732</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>121</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9766</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2.6562</v>
+      </c>
+      <c r="G118" t="n">
+        <v>6.5572</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>122</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9621</v>
+      </c>
+      <c r="F119" t="n">
+        <v>3.3734</v>
+      </c>
+      <c r="G119" t="n">
+        <v>6.8124</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>123</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.9626</v>
+      </c>
+      <c r="F120" t="n">
+        <v>3.1486</v>
+      </c>
+      <c r="G120" t="n">
+        <v>7.5671</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>124</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.9626</v>
+      </c>
+      <c r="F121" t="n">
+        <v>3.1486</v>
+      </c>
+      <c r="G121" t="n">
+        <v>7.5671</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>125</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9689</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2.7468</v>
+      </c>
+      <c r="G122" t="n">
+        <v>6.6415</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>126</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9623</v>
+      </c>
+      <c r="F123" t="n">
+        <v>3.3756</v>
+      </c>
+      <c r="G123" t="n">
+        <v>6.807</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>127</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.9809</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2.6421</v>
+      </c>
+      <c r="G124" t="n">
+        <v>6.6011</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>128</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9513</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3.2415</v>
+      </c>
+      <c r="G125" t="n">
+        <v>6.8267</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>129</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.9756</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2.6694</v>
+      </c>
+      <c r="G126" t="n">
+        <v>7.2649</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>130</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9611</v>
+      </c>
+      <c r="F127" t="n">
+        <v>3.3133</v>
+      </c>
+      <c r="G127" t="n">
+        <v>7.8337</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>131</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0.9621</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3.1482</v>
+      </c>
+      <c r="G128" t="n">
+        <v>7.2555</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>132</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0.9751</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2.6851</v>
+      </c>
+      <c r="G129" t="n">
+        <v>7.2731</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>133</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 27))</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3.1615</v>
+      </c>
+      <c r="G130" t="n">
+        <v>7.2544</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>134</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0.9752999999999999</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2.6649</v>
+      </c>
+      <c r="G131" t="n">
+        <v>7.2748</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>135</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0.9622000000000001</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3.1391</v>
+      </c>
+      <c r="G132" t="n">
+        <v>7.2592</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>136</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 17))</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0.9725</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2.7032</v>
+      </c>
+      <c r="G133" t="n">
+        <v>7.2708</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>137</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 19))</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="F134" t="n">
+        <v>3.1368</v>
+      </c>
+      <c r="G134" t="n">
+        <v>7.2875</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>138</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0.9752999999999999</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.6687</v>
+      </c>
+      <c r="G135" t="n">
+        <v>7.2796</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>139</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="G136" t="n">
+        <v>7.2883</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>140</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,2,11))</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0.9702</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2.7603</v>
+      </c>
+      <c r="G137" t="n">
+        <v>6.6531</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>141</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2.6667</v>
+      </c>
+      <c r="G138" t="n">
+        <v>6.6494</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>142</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0.9712</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2.7109</v>
+      </c>
+      <c r="G139" t="n">
+        <v>6.6404</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>143</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2.5053</v>
+      </c>
+      <c r="G140" t="n">
+        <v>6.4068</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>144</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="F141" t="n">
+        <v>2.4246</v>
+      </c>
+      <c r="G141" t="n">
+        <v>6.4417</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>145</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2.6667</v>
+      </c>
+      <c r="G142" t="n">
+        <v>6.6494</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>146</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,25))</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="F143" t="n">
+        <v>2.8022</v>
+      </c>
+      <c r="G143" t="n">
+        <v>6.7299</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>147</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="F144" t="n">
+        <v>2.7974</v>
+      </c>
+      <c r="G144" t="n">
+        <v>6.738</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>148</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="F145" t="n">
+        <v>2.4246</v>
+      </c>
+      <c r="G145" t="n">
+        <v>6.4417</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>149</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0.9588</v>
+      </c>
+      <c r="F146" t="n">
+        <v>3.3838</v>
+      </c>
+      <c r="G146" t="n">
+        <v>7.8793</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>150</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0.9627</v>
+      </c>
+      <c r="F147" t="n">
+        <v>3.2902</v>
+      </c>
+      <c r="G147" t="n">
+        <v>7.9239</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>151</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 27))</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0.9696</v>
+      </c>
+      <c r="F148" t="n">
+        <v>3.0505</v>
+      </c>
+      <c r="G148" t="n">
+        <v>7.9005</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>152</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0.9611</v>
+      </c>
+      <c r="F149" t="n">
+        <v>3.3181</v>
+      </c>
+      <c r="G149" t="n">
+        <v>7.8946</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>153</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0.9587</v>
+      </c>
+      <c r="F150" t="n">
+        <v>3.3786</v>
+      </c>
+      <c r="G150" t="n">
+        <v>7.8401</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>154</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 17))</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0.9609</v>
+      </c>
+      <c r="F151" t="n">
+        <v>3.2998</v>
+      </c>
+      <c r="G151" t="n">
+        <v>7.8359</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>155</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 19))</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0.9675</v>
+      </c>
+      <c r="F152" t="n">
+        <v>3.0747</v>
+      </c>
+      <c r="G152" t="n">
+        <v>7.8138</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>156</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0.9673</v>
+      </c>
+      <c r="F153" t="n">
+        <v>3.0973</v>
+      </c>
+      <c r="G153" t="n">
+        <v>7.8162</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>157</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="F154" t="n">
+        <v>3.1162</v>
+      </c>
+      <c r="G154" t="n">
+        <v>7.8353</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>158</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0.9788</v>
+      </c>
+      <c r="F155" t="n">
+        <v>2.5055</v>
+      </c>
+      <c r="G155" t="n">
+        <v>6.4333</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>159</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,25))</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2.4181</v>
+      </c>
+      <c r="G156" t="n">
+        <v>6.4617</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>160</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="G157" t="n">
+        <v>6.5311</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>161</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="F158" t="n">
+        <v>2.205</v>
+      </c>
+      <c r="G158" t="n">
+        <v>5.6051</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>162</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="F159" t="n">
+        <v>2.9495</v>
+      </c>
+      <c r="G159" t="n">
+        <v>7.275</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>163</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0.9614</v>
+      </c>
+      <c r="F160" t="n">
+        <v>3.4271</v>
+      </c>
+      <c r="G160" t="n">
+        <v>8.1286</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>164</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0.9537</v>
+      </c>
+      <c r="F161" t="n">
+        <v>3.7082</v>
+      </c>
+      <c r="G161" t="n">
+        <v>8.135899999999999</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>165</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0.9692</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2.8768</v>
+      </c>
+      <c r="G162" t="n">
+        <v>7.2846</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>166</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0.9691</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2.7986</v>
+      </c>
+      <c r="G163" t="n">
+        <v>6.7591</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>167</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="F164" t="n">
+        <v>2.5516</v>
+      </c>
+      <c r="G164" t="n">
+        <v>6.403</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>168</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0.9513</v>
+      </c>
+      <c r="F165" t="n">
+        <v>3.2415</v>
+      </c>
+      <c r="G165" t="n">
+        <v>6.8267</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>169</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0.9147999999999999</v>
+      </c>
+      <c r="F166" t="n">
+        <v>4.1177</v>
+      </c>
+      <c r="G166" t="n">
+        <v>7.074</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>170</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0.9704</v>
+      </c>
+      <c r="F167" t="n">
+        <v>2.7079</v>
+      </c>
+      <c r="G167" t="n">
+        <v>6.5684</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>171</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0.9738</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2.9207</v>
+      </c>
+      <c r="G168" t="n">
+        <v>6.7816</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>172</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0.9835</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2.2512</v>
+      </c>
+      <c r="G169" t="n">
+        <v>5.9447</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>173</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0.9691</v>
+      </c>
+      <c r="F170" t="n">
+        <v>3.3713</v>
+      </c>
+      <c r="G170" t="n">
+        <v>7.2117</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>174</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="F171" t="n">
+        <v>2.6953</v>
+      </c>
+      <c r="G171" t="n">
+        <v>6.7041</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>eau</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>175</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('sder',c(1,3,31)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0.9738</v>
+      </c>
+      <c r="F172" t="n">
+        <v>2.7303</v>
+      </c>
+      <c r="G172" t="n">
+        <v>7.029</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/eau/RANDOMSEARCH_DETAILS_eau.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/eau/RANDOMSEARCH_DETAILS_eau.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>RMSEC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RMSECV</t>
         </is>
@@ -476,9 +481,12 @@
         <v>0.9849</v>
       </c>
       <c r="F2" t="n">
+        <v>1.3547</v>
+      </c>
+      <c r="G2" t="n">
         <v>2.1723</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>5.8032</v>
       </c>
     </row>
@@ -505,9 +513,12 @@
         <v>0.9857</v>
       </c>
       <c r="F3" t="n">
+        <v>1.3352</v>
+      </c>
+      <c r="G3" t="n">
         <v>2.0685</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>5.6412</v>
       </c>
     </row>
@@ -534,9 +545,12 @@
         <v>0.922</v>
       </c>
       <c r="F4" t="n">
+        <v>1.4899</v>
+      </c>
+      <c r="G4" t="n">
         <v>3.9488</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>6.8195</v>
       </c>
     </row>
@@ -563,9 +577,12 @@
         <v>0.9712</v>
       </c>
       <c r="F5" t="n">
+        <v>1.6505</v>
+      </c>
+      <c r="G5" t="n">
         <v>2.8848</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>7.8581</v>
       </c>
     </row>
@@ -592,9 +609,12 @@
         <v>0.9578</v>
       </c>
       <c r="F6" t="n">
+        <v>1.6633</v>
+      </c>
+      <c r="G6" t="n">
         <v>3.393</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>7.9352</v>
       </c>
     </row>
@@ -621,9 +641,12 @@
         <v>0.9717</v>
       </c>
       <c r="F7" t="n">
+        <v>1.5834</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.8433</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>7.4422</v>
       </c>
     </row>
@@ -650,9 +673,12 @@
         <v>0.9723000000000001</v>
       </c>
       <c r="F8" t="n">
+        <v>1.5778</v>
+      </c>
+      <c r="G8" t="n">
         <v>2.7956</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>7.4061</v>
       </c>
     </row>
@@ -679,9 +705,12 @@
         <v>0.9835</v>
       </c>
       <c r="F9" t="n">
+        <v>1.4624</v>
+      </c>
+      <c r="G9" t="n">
         <v>2.344</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>6.6258</v>
       </c>
     </row>
@@ -708,9 +737,12 @@
         <v>0.9728</v>
       </c>
       <c r="F10" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="G10" t="n">
         <v>2.7799</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>7.427</v>
       </c>
     </row>
@@ -737,9 +769,12 @@
         <v>0.9618</v>
       </c>
       <c r="F11" t="n">
+        <v>1.5808</v>
+      </c>
+      <c r="G11" t="n">
         <v>3.2396</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>7.4257</v>
       </c>
     </row>
@@ -766,9 +801,12 @@
         <v>0.9728</v>
       </c>
       <c r="F12" t="n">
+        <v>1.5848</v>
+      </c>
+      <c r="G12" t="n">
         <v>2.7861</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>7.4512</v>
       </c>
     </row>
@@ -795,9 +833,12 @@
         <v>0.9724</v>
       </c>
       <c r="F13" t="n">
+        <v>1.5848</v>
+      </c>
+      <c r="G13" t="n">
         <v>2.792</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>7.4513</v>
       </c>
     </row>
@@ -824,9 +865,12 @@
         <v>0.9728</v>
       </c>
       <c r="F14" t="n">
+        <v>1.582</v>
+      </c>
+      <c r="G14" t="n">
         <v>2.7905</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>7.4331</v>
       </c>
     </row>
@@ -853,9 +897,12 @@
         <v>0.9725</v>
       </c>
       <c r="F15" t="n">
+        <v>1.5832</v>
+      </c>
+      <c r="G15" t="n">
         <v>2.7905</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>7.4406</v>
       </c>
     </row>
@@ -882,9 +929,12 @@
         <v>0.9724</v>
       </c>
       <c r="F16" t="n">
+        <v>1.5822</v>
+      </c>
+      <c r="G16" t="n">
         <v>2.7983</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>7.4343</v>
       </c>
     </row>
@@ -911,9 +961,12 @@
         <v>0.9731</v>
       </c>
       <c r="F17" t="n">
+        <v>1.5796</v>
+      </c>
+      <c r="G17" t="n">
         <v>2.7657</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>7.4179</v>
       </c>
     </row>
@@ -940,9 +993,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F18" t="n">
+        <v>1.458</v>
+      </c>
+      <c r="G18" t="n">
         <v>2.4646</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>6.5941</v>
       </c>
     </row>
@@ -969,9 +1025,12 @@
         <v>0.97</v>
       </c>
       <c r="F19" t="n">
+        <v>1.4611</v>
+      </c>
+      <c r="G19" t="n">
         <v>2.7406</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>6.6163</v>
       </c>
     </row>
@@ -998,9 +1057,12 @@
         <v>0.9714</v>
       </c>
       <c r="F20" t="n">
+        <v>1.4761</v>
+      </c>
+      <c r="G20" t="n">
         <v>2.7103</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>6.7229</v>
       </c>
     </row>
@@ -1027,9 +1089,12 @@
         <v>0.9684</v>
       </c>
       <c r="F21" t="n">
+        <v>1.489</v>
+      </c>
+      <c r="G21" t="n">
         <v>2.8653</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>6.8132</v>
       </c>
     </row>
@@ -1056,9 +1121,12 @@
         <v>0.9747</v>
       </c>
       <c r="F22" t="n">
+        <v>1.5005</v>
+      </c>
+      <c r="G22" t="n">
         <v>2.6108</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>6.8931</v>
       </c>
     </row>
@@ -1085,9 +1153,12 @@
         <v>0.9729</v>
       </c>
       <c r="F23" t="n">
+        <v>1.5079</v>
+      </c>
+      <c r="G23" t="n">
         <v>2.6976</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>6.9435</v>
       </c>
     </row>
@@ -1114,9 +1185,12 @@
         <v>0.9648</v>
       </c>
       <c r="F24" t="n">
+        <v>1.5282</v>
+      </c>
+      <c r="G24" t="n">
         <v>3.0088</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>7.0814</v>
       </c>
     </row>
@@ -1143,9 +1217,12 @@
         <v>0.9611</v>
       </c>
       <c r="F25" t="n">
+        <v>1.534</v>
+      </c>
+      <c r="G25" t="n">
         <v>3.1526</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>7.1203</v>
       </c>
     </row>
@@ -1172,9 +1249,12 @@
         <v>0.9758</v>
       </c>
       <c r="F26" t="n">
+        <v>1.4604</v>
+      </c>
+      <c r="G26" t="n">
         <v>2.5894</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>6.611</v>
       </c>
     </row>
@@ -1201,9 +1281,12 @@
         <v>0.9742</v>
       </c>
       <c r="F27" t="n">
+        <v>1.4559</v>
+      </c>
+      <c r="G27" t="n">
         <v>2.6873</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>6.5785</v>
       </c>
     </row>
@@ -1230,9 +1313,12 @@
         <v>0.9758</v>
       </c>
       <c r="F28" t="n">
+        <v>1.4508</v>
+      </c>
+      <c r="G28" t="n">
         <v>2.6004</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>6.5423</v>
       </c>
     </row>
@@ -1259,9 +1345,12 @@
         <v>0.9742</v>
       </c>
       <c r="F29" t="n">
+        <v>1.4566</v>
+      </c>
+      <c r="G29" t="n">
         <v>2.6156</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>6.5838</v>
       </c>
     </row>
@@ -1288,9 +1377,12 @@
         <v>0.9722</v>
       </c>
       <c r="F30" t="n">
+        <v>1.4708</v>
+      </c>
+      <c r="G30" t="n">
         <v>2.7233</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>6.6851</v>
       </c>
     </row>
@@ -1317,9 +1409,12 @@
         <v>0.9752</v>
       </c>
       <c r="F31" t="n">
+        <v>1.4782</v>
+      </c>
+      <c r="G31" t="n">
         <v>2.5863</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>6.7375</v>
       </c>
     </row>
@@ -1346,9 +1441,12 @@
         <v>0.9661</v>
       </c>
       <c r="F32" t="n">
+        <v>1.4989</v>
+      </c>
+      <c r="G32" t="n">
         <v>2.9307</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>6.8819</v>
       </c>
     </row>
@@ -1375,9 +1473,12 @@
         <v>0.9736</v>
       </c>
       <c r="F33" t="n">
+        <v>1.5049</v>
+      </c>
+      <c r="G33" t="n">
         <v>2.6523</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>6.923</v>
       </c>
     </row>
@@ -1404,9 +1505,12 @@
         <v>0.9779</v>
       </c>
       <c r="F34" t="n">
+        <v>1.4885</v>
+      </c>
+      <c r="G34" t="n">
         <v>2.8199</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>6.8102</v>
       </c>
     </row>
@@ -1433,9 +1537,12 @@
         <v>0.9629</v>
       </c>
       <c r="F35" t="n">
+        <v>1.4789</v>
+      </c>
+      <c r="G35" t="n">
         <v>3.2711</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>6.7429</v>
       </c>
     </row>
@@ -1462,9 +1569,12 @@
         <v>0.9846</v>
       </c>
       <c r="F36" t="n">
+        <v>1.4643</v>
+      </c>
+      <c r="G36" t="n">
         <v>2.4375</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>6.6389</v>
       </c>
     </row>
@@ -1491,9 +1601,12 @@
         <v>0.984</v>
       </c>
       <c r="F37" t="n">
+        <v>1.4783</v>
+      </c>
+      <c r="G37" t="n">
         <v>2.4229</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>6.7388</v>
       </c>
     </row>
@@ -1520,9 +1633,12 @@
         <v>0.9767</v>
       </c>
       <c r="F38" t="n">
+        <v>1.4666</v>
+      </c>
+      <c r="G38" t="n">
         <v>2.7033</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>6.6555</v>
       </c>
     </row>
@@ -1549,9 +1665,12 @@
         <v>0.9843</v>
       </c>
       <c r="F39" t="n">
+        <v>1.4809</v>
+      </c>
+      <c r="G39" t="n">
         <v>2.4231</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>6.7567</v>
       </c>
     </row>
@@ -1578,9 +1697,12 @@
         <v>0.9775</v>
       </c>
       <c r="F40" t="n">
+        <v>1.4859</v>
+      </c>
+      <c r="G40" t="n">
         <v>2.703</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>6.7916</v>
       </c>
     </row>
@@ -1607,9 +1729,12 @@
         <v>0.9644</v>
       </c>
       <c r="F41" t="n">
+        <v>1.4895</v>
+      </c>
+      <c r="G41" t="n">
         <v>3.2334</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>6.8171</v>
       </c>
     </row>
@@ -1636,9 +1761,12 @@
         <v>0.9627</v>
       </c>
       <c r="F42" t="n">
+        <v>1.4783</v>
+      </c>
+      <c r="G42" t="n">
         <v>3.2728</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>6.7383</v>
       </c>
     </row>
@@ -1665,9 +1793,12 @@
         <v>0.9813</v>
       </c>
       <c r="F43" t="n">
+        <v>1.4643</v>
+      </c>
+      <c r="G43" t="n">
         <v>2.5948</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>6.6395</v>
       </c>
     </row>
@@ -1694,9 +1825,12 @@
         <v>0.985</v>
       </c>
       <c r="F44" t="n">
+        <v>1.4805</v>
+      </c>
+      <c r="G44" t="n">
         <v>2.3958</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>6.7537</v>
       </c>
     </row>
@@ -1723,9 +1857,12 @@
         <v>0.9768</v>
       </c>
       <c r="F45" t="n">
+        <v>1.4697</v>
+      </c>
+      <c r="G45" t="n">
         <v>2.7082</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>6.6776</v>
       </c>
     </row>
@@ -1752,9 +1889,12 @@
         <v>0.9782</v>
       </c>
       <c r="F46" t="n">
+        <v>1.4867</v>
+      </c>
+      <c r="G46" t="n">
         <v>2.6999</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>6.7973</v>
       </c>
     </row>
@@ -1781,9 +1921,12 @@
         <v>0.9781</v>
       </c>
       <c r="F47" t="n">
+        <v>1.4858</v>
+      </c>
+      <c r="G47" t="n">
         <v>2.6879</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>6.7913</v>
       </c>
     </row>
@@ -1810,9 +1953,12 @@
         <v>0.9862</v>
       </c>
       <c r="F48" t="n">
+        <v>1.4668</v>
+      </c>
+      <c r="G48" t="n">
         <v>2.4051</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>6.6567</v>
       </c>
     </row>
@@ -1839,9 +1985,12 @@
         <v>0.9814000000000001</v>
       </c>
       <c r="F49" t="n">
+        <v>1.4542</v>
+      </c>
+      <c r="G49" t="n">
         <v>2.5386</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>6.5669</v>
       </c>
     </row>
@@ -1868,9 +2017,12 @@
         <v>0.9841</v>
       </c>
       <c r="F50" t="n">
+        <v>1.3279</v>
+      </c>
+      <c r="G50" t="n">
         <v>2.0631</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>5.5792</v>
       </c>
     </row>
@@ -1897,9 +2049,12 @@
         <v>0.9747</v>
       </c>
       <c r="F51" t="n">
+        <v>1.5343</v>
+      </c>
+      <c r="G51" t="n">
         <v>2.9004</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>7.1222</v>
       </c>
     </row>
@@ -1926,9 +2081,12 @@
         <v>0.9742</v>
       </c>
       <c r="F52" t="n">
+        <v>1.5552</v>
+      </c>
+      <c r="G52" t="n">
         <v>2.928</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>7.26</v>
       </c>
     </row>
@@ -1955,9 +2113,12 @@
         <v>0.9831</v>
       </c>
       <c r="F53" t="n">
+        <v>1.4893</v>
+      </c>
+      <c r="G53" t="n">
         <v>2.4269</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>6.8156</v>
       </c>
     </row>
@@ -1984,9 +2145,12 @@
         <v>0.9756</v>
       </c>
       <c r="F54" t="n">
+        <v>1.5095</v>
+      </c>
+      <c r="G54" t="n">
         <v>2.7161</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>6.955</v>
       </c>
     </row>
@@ -2013,9 +2177,12 @@
         <v>0.984</v>
       </c>
       <c r="F55" t="n">
+        <v>1.3818</v>
+      </c>
+      <c r="G55" t="n">
         <v>2.1524</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>6.0202</v>
       </c>
     </row>
@@ -2042,9 +2209,12 @@
         <v>0.9829</v>
       </c>
       <c r="F56" t="n">
+        <v>1.3469</v>
+      </c>
+      <c r="G56" t="n">
         <v>2.2143</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>5.739</v>
       </c>
     </row>
@@ -2071,9 +2241,12 @@
         <v>0.9842</v>
       </c>
       <c r="F57" t="n">
+        <v>1.3177</v>
+      </c>
+      <c r="G57" t="n">
         <v>2.1137</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>5.4916</v>
       </c>
     </row>
@@ -2100,9 +2273,12 @@
         <v>0.9582000000000001</v>
       </c>
       <c r="F58" t="n">
+        <v>1.6701</v>
+      </c>
+      <c r="G58" t="n">
         <v>3.3829</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>7.9759</v>
       </c>
     </row>
@@ -2129,9 +2305,12 @@
         <v>0.9589</v>
       </c>
       <c r="F59" t="n">
+        <v>1.6693</v>
+      </c>
+      <c r="G59" t="n">
         <v>3.3735</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>7.9709</v>
       </c>
     </row>
@@ -2158,9 +2337,12 @@
         <v>0.958</v>
       </c>
       <c r="F60" t="n">
+        <v>1.6701</v>
+      </c>
+      <c r="G60" t="n">
         <v>3.3885</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>7.9761</v>
       </c>
     </row>
@@ -2187,9 +2369,12 @@
         <v>0.9566</v>
       </c>
       <c r="F61" t="n">
+        <v>1.6774</v>
+      </c>
+      <c r="G61" t="n">
         <v>3.412</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>8.0192</v>
       </c>
     </row>
@@ -2216,9 +2401,12 @@
         <v>0.9792</v>
       </c>
       <c r="F62" t="n">
+        <v>1.3816</v>
+      </c>
+      <c r="G62" t="n">
         <v>2.4255</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>6.0189</v>
       </c>
     </row>
@@ -2245,9 +2433,12 @@
         <v>0.978</v>
       </c>
       <c r="F63" t="n">
+        <v>1.3903</v>
+      </c>
+      <c r="G63" t="n">
         <v>2.4553</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>6.0868</v>
       </c>
     </row>
@@ -2274,9 +2465,12 @@
         <v>0.9772</v>
       </c>
       <c r="F64" t="n">
+        <v>1.3964</v>
+      </c>
+      <c r="G64" t="n">
         <v>2.5117</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>6.1346</v>
       </c>
     </row>
@@ -2303,9 +2497,12 @@
         <v>0.98</v>
       </c>
       <c r="F65" t="n">
+        <v>1.4007</v>
+      </c>
+      <c r="G65" t="n">
         <v>2.2955</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>6.1676</v>
       </c>
     </row>
@@ -2332,9 +2529,12 @@
         <v>0.9853</v>
       </c>
       <c r="F66" t="n">
+        <v>1.3098</v>
+      </c>
+      <c r="G66" t="n">
         <v>1.9944</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>5.4229</v>
       </c>
     </row>
@@ -2361,9 +2561,12 @@
         <v>0.9833</v>
       </c>
       <c r="F67" t="n">
+        <v>1.3269</v>
+      </c>
+      <c r="G67" t="n">
         <v>2.1416</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>5.5704</v>
       </c>
     </row>
@@ -2390,9 +2593,12 @@
         <v>0.9825</v>
       </c>
       <c r="F68" t="n">
+        <v>1.3278</v>
+      </c>
+      <c r="G68" t="n">
         <v>2.156</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>5.5785</v>
       </c>
     </row>
@@ -2419,9 +2625,12 @@
         <v>0.9726</v>
       </c>
       <c r="F69" t="n">
+        <v>1.4504</v>
+      </c>
+      <c r="G69" t="n">
         <v>2.7223</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>6.539</v>
       </c>
     </row>
@@ -2448,9 +2657,12 @@
         <v>0.9671999999999999</v>
       </c>
       <c r="F70" t="n">
+        <v>1.454</v>
+      </c>
+      <c r="G70" t="n">
         <v>2.8527</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>6.5651</v>
       </c>
     </row>
@@ -2477,9 +2689,12 @@
         <v>0.9748</v>
       </c>
       <c r="F71" t="n">
+        <v>1.4288</v>
+      </c>
+      <c r="G71" t="n">
         <v>2.6176</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>6.3804</v>
       </c>
     </row>
@@ -2506,9 +2721,12 @@
         <v>0.9738</v>
       </c>
       <c r="F72" t="n">
+        <v>1.4371</v>
+      </c>
+      <c r="G72" t="n">
         <v>2.6509</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>6.4414</v>
       </c>
     </row>
@@ -2535,9 +2753,12 @@
         <v>0.9784</v>
       </c>
       <c r="F73" t="n">
+        <v>1.5551</v>
+      </c>
+      <c r="G73" t="n">
         <v>2.9238</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>7.2592</v>
       </c>
     </row>
@@ -2564,9 +2785,12 @@
         <v>0.9782</v>
       </c>
       <c r="F74" t="n">
+        <v>1.5949</v>
+      </c>
+      <c r="G74" t="n">
         <v>2.9899</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>7.5148</v>
       </c>
     </row>
@@ -2593,9 +2817,12 @@
         <v>0.9491000000000001</v>
       </c>
       <c r="F75" t="n">
+        <v>1.6108</v>
+      </c>
+      <c r="G75" t="n">
         <v>3.6706</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>7.6149</v>
       </c>
     </row>
@@ -2622,9 +2849,12 @@
         <v>0.9491000000000001</v>
       </c>
       <c r="F76" t="n">
+        <v>1.6108</v>
+      </c>
+      <c r="G76" t="n">
         <v>3.6706</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>7.6149</v>
       </c>
     </row>
@@ -2651,9 +2881,12 @@
         <v>0.9703000000000001</v>
       </c>
       <c r="F77" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="G77" t="n">
         <v>2.9525</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>8.0817</v>
       </c>
     </row>
@@ -2680,9 +2913,12 @@
         <v>0.9621</v>
       </c>
       <c r="F78" t="n">
+        <v>1.6858</v>
+      </c>
+      <c r="G78" t="n">
         <v>3.2336</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>8.068899999999999</v>
       </c>
     </row>
@@ -2709,9 +2945,12 @@
         <v>0.9611</v>
       </c>
       <c r="F79" t="n">
+        <v>1.6826</v>
+      </c>
+      <c r="G79" t="n">
         <v>3.3536</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>8.0502</v>
       </c>
     </row>
@@ -2738,9 +2977,12 @@
         <v>0.97</v>
       </c>
       <c r="F80" t="n">
+        <v>1.6868</v>
+      </c>
+      <c r="G80" t="n">
         <v>2.9679</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>8.074999999999999</v>
       </c>
     </row>
@@ -2767,9 +3009,12 @@
         <v>0.9829</v>
       </c>
       <c r="F81" t="n">
+        <v>1.3504</v>
+      </c>
+      <c r="G81" t="n">
         <v>2.1298</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>5.7675</v>
       </c>
     </row>
@@ -2796,9 +3041,12 @@
         <v>0.982</v>
       </c>
       <c r="F82" t="n">
+        <v>1.3583</v>
+      </c>
+      <c r="G82" t="n">
         <v>2.1805</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>5.8321</v>
       </c>
     </row>
@@ -2825,9 +3073,12 @@
         <v>0.9681999999999999</v>
       </c>
       <c r="F83" t="n">
+        <v>1.6012</v>
+      </c>
+      <c r="G83" t="n">
         <v>3.0943</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>7.5546</v>
       </c>
     </row>
@@ -2854,9 +3105,12 @@
         <v>0.9482</v>
       </c>
       <c r="F84" t="n">
+        <v>1.6072</v>
+      </c>
+      <c r="G84" t="n">
         <v>3.6807</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>7.5922</v>
       </c>
     </row>
@@ -2883,9 +3137,12 @@
         <v>0.9678</v>
       </c>
       <c r="F85" t="n">
+        <v>1.6044</v>
+      </c>
+      <c r="G85" t="n">
         <v>3.092</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>7.5748</v>
       </c>
     </row>
@@ -2912,9 +3169,12 @@
         <v>0.9761</v>
       </c>
       <c r="F86" t="n">
+        <v>1.4595</v>
+      </c>
+      <c r="G86" t="n">
         <v>2.6047</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>6.6044</v>
       </c>
     </row>
@@ -2941,9 +3201,12 @@
         <v>0.9754</v>
       </c>
       <c r="F87" t="n">
+        <v>1.4548</v>
+      </c>
+      <c r="G87" t="n">
         <v>2.5908</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>6.5708</v>
       </c>
     </row>
@@ -2970,9 +3233,12 @@
         <v>0.9737</v>
       </c>
       <c r="F88" t="n">
+        <v>1.4482</v>
+      </c>
+      <c r="G88" t="n">
         <v>2.6315</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>6.5228</v>
       </c>
     </row>
@@ -2999,9 +3265,12 @@
         <v>0.9748</v>
       </c>
       <c r="F89" t="n">
+        <v>1.4634</v>
+      </c>
+      <c r="G89" t="n">
         <v>2.6146</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>6.6326</v>
       </c>
     </row>
@@ -3028,9 +3297,12 @@
         <v>0.9812</v>
       </c>
       <c r="F90" t="n">
+        <v>1.4646</v>
+      </c>
+      <c r="G90" t="n">
         <v>2.5971</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>6.6414</v>
       </c>
     </row>
@@ -3057,9 +3329,12 @@
         <v>0.985</v>
       </c>
       <c r="F91" t="n">
+        <v>1.4805</v>
+      </c>
+      <c r="G91" t="n">
         <v>2.3984</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>6.7543</v>
       </c>
     </row>
@@ -3086,9 +3361,12 @@
         <v>0.9737</v>
       </c>
       <c r="F92" t="n">
+        <v>1.4482</v>
+      </c>
+      <c r="G92" t="n">
         <v>2.6315</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>6.5228</v>
       </c>
     </row>
@@ -3115,9 +3393,12 @@
         <v>0.985</v>
       </c>
       <c r="F93" t="n">
+        <v>1.4805</v>
+      </c>
+      <c r="G93" t="n">
         <v>2.3984</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>6.7543</v>
       </c>
     </row>
@@ -3144,9 +3425,12 @@
         <v>0.922</v>
       </c>
       <c r="F94" t="n">
+        <v>1.4899</v>
+      </c>
+      <c r="G94" t="n">
         <v>3.9488</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>6.8195</v>
       </c>
     </row>
@@ -3173,9 +3457,12 @@
         <v>0.9407</v>
       </c>
       <c r="F95" t="n">
+        <v>1.5222</v>
+      </c>
+      <c r="G95" t="n">
         <v>3.5304</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>7.041</v>
       </c>
     </row>
@@ -3202,9 +3489,12 @@
         <v>0.9214</v>
       </c>
       <c r="F96" t="n">
+        <v>1.4886</v>
+      </c>
+      <c r="G96" t="n">
         <v>3.9606</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>6.8107</v>
       </c>
     </row>
@@ -3231,9 +3521,12 @@
         <v>0.9209000000000001</v>
       </c>
       <c r="F97" t="n">
+        <v>1.4894</v>
+      </c>
+      <c r="G97" t="n">
         <v>3.972</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>6.816</v>
       </c>
     </row>
@@ -3260,9 +3553,12 @@
         <v>0.9764</v>
       </c>
       <c r="F98" t="n">
+        <v>1.4457</v>
+      </c>
+      <c r="G98" t="n">
         <v>2.6991</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>6.5046</v>
       </c>
     </row>
@@ -3289,9 +3585,12 @@
         <v>0.9776</v>
       </c>
       <c r="F99" t="n">
+        <v>1.4548</v>
+      </c>
+      <c r="G99" t="n">
         <v>2.6033</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>6.571</v>
       </c>
     </row>
@@ -3318,9 +3617,12 @@
         <v>0.9746</v>
       </c>
       <c r="F100" t="n">
+        <v>1.4672</v>
+      </c>
+      <c r="G100" t="n">
         <v>2.7024</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>6.6596</v>
       </c>
     </row>
@@ -3347,9 +3649,12 @@
         <v>0.982</v>
       </c>
       <c r="F101" t="n">
+        <v>1.4738</v>
+      </c>
+      <c r="G101" t="n">
         <v>2.3796</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>6.7068</v>
       </c>
     </row>
@@ -3376,9 +3681,12 @@
         <v>0.9752999999999999</v>
       </c>
       <c r="F102" t="n">
+        <v>1.4739</v>
+      </c>
+      <c r="G102" t="n">
         <v>2.628</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>6.7076</v>
       </c>
     </row>
@@ -3405,9 +3713,12 @@
         <v>0.978</v>
       </c>
       <c r="F103" t="n">
+        <v>1.4945</v>
+      </c>
+      <c r="G103" t="n">
         <v>2.733</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>6.8517</v>
       </c>
     </row>
@@ -3434,9 +3745,12 @@
         <v>0.978</v>
       </c>
       <c r="F104" t="n">
+        <v>1.4461</v>
+      </c>
+      <c r="G104" t="n">
         <v>2.6357</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>6.5076</v>
       </c>
     </row>
@@ -3463,9 +3777,12 @@
         <v>0.9766</v>
       </c>
       <c r="F105" t="n">
+        <v>1.4529</v>
+      </c>
+      <c r="G105" t="n">
         <v>2.6562</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>6.5572</v>
       </c>
     </row>
@@ -3492,9 +3809,12 @@
         <v>0.9776</v>
       </c>
       <c r="F106" t="n">
+        <v>1.4534</v>
+      </c>
+      <c r="G106" t="n">
         <v>2.5694</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>6.5608</v>
       </c>
     </row>
@@ -3521,9 +3841,12 @@
         <v>0.9724</v>
       </c>
       <c r="F107" t="n">
+        <v>1.4705</v>
+      </c>
+      <c r="G107" t="n">
         <v>2.7994</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>6.6836</v>
       </c>
     </row>
@@ -3550,9 +3873,12 @@
         <v>0.9796</v>
       </c>
       <c r="F108" t="n">
+        <v>1.5402</v>
+      </c>
+      <c r="G108" t="n">
         <v>2.7218</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>7.1614</v>
       </c>
     </row>
@@ -3579,9 +3905,12 @@
         <v>0.9806</v>
       </c>
       <c r="F109" t="n">
+        <v>1.4887</v>
+      </c>
+      <c r="G109" t="n">
         <v>2.6966</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>6.8116</v>
       </c>
     </row>
@@ -3608,9 +3937,12 @@
         <v>0.9805</v>
       </c>
       <c r="F110" t="n">
+        <v>1.4454</v>
+      </c>
+      <c r="G110" t="n">
         <v>2.5965</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>6.5024</v>
       </c>
     </row>
@@ -3637,9 +3969,12 @@
         <v>0.9768</v>
       </c>
       <c r="F111" t="n">
+        <v>1.4397</v>
+      </c>
+      <c r="G111" t="n">
         <v>2.6509</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>6.4606</v>
       </c>
     </row>
@@ -3666,9 +4001,12 @@
         <v>0.9795</v>
       </c>
       <c r="F112" t="n">
+        <v>1.5396</v>
+      </c>
+      <c r="G112" t="n">
         <v>2.8263</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>7.1571</v>
       </c>
     </row>
@@ -3695,9 +4033,12 @@
         <v>0.9621</v>
       </c>
       <c r="F113" t="n">
+        <v>1.4889</v>
+      </c>
+      <c r="G113" t="n">
         <v>3.3734</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>6.8124</v>
       </c>
     </row>
@@ -3724,9 +4065,12 @@
         <v>0.9804</v>
       </c>
       <c r="F114" t="n">
+        <v>1.4505</v>
+      </c>
+      <c r="G114" t="n">
         <v>2.6002</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>6.5395</v>
       </c>
     </row>
@@ -3753,9 +4097,12 @@
         <v>0.9733000000000001</v>
       </c>
       <c r="F115" t="n">
+        <v>1.4319</v>
+      </c>
+      <c r="G115" t="n">
         <v>2.7357</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>6.4034</v>
       </c>
     </row>
@@ -3782,9 +4129,12 @@
         <v>0.9697</v>
       </c>
       <c r="F116" t="n">
+        <v>1.3955</v>
+      </c>
+      <c r="G116" t="n">
         <v>2.666</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>6.1272</v>
       </c>
     </row>
@@ -3811,9 +4161,12 @@
         <v>0.9731</v>
       </c>
       <c r="F117" t="n">
+        <v>1.4014</v>
+      </c>
+      <c r="G117" t="n">
         <v>2.5903</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>6.1732</v>
       </c>
     </row>
@@ -3840,9 +4193,12 @@
         <v>0.9766</v>
       </c>
       <c r="F118" t="n">
+        <v>1.4529</v>
+      </c>
+      <c r="G118" t="n">
         <v>2.6562</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>6.5572</v>
       </c>
     </row>
@@ -3869,9 +4225,12 @@
         <v>0.9621</v>
       </c>
       <c r="F119" t="n">
+        <v>1.4889</v>
+      </c>
+      <c r="G119" t="n">
         <v>3.3734</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>6.8124</v>
       </c>
     </row>
@@ -3898,9 +4257,12 @@
         <v>0.9626</v>
       </c>
       <c r="F120" t="n">
+        <v>1.6032</v>
+      </c>
+      <c r="G120" t="n">
         <v>3.1486</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>7.5671</v>
       </c>
     </row>
@@ -3927,9 +4289,12 @@
         <v>0.9626</v>
       </c>
       <c r="F121" t="n">
+        <v>1.6032</v>
+      </c>
+      <c r="G121" t="n">
         <v>3.1486</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>7.5671</v>
       </c>
     </row>
@@ -3956,9 +4321,12 @@
         <v>0.9689</v>
       </c>
       <c r="F122" t="n">
+        <v>1.4646</v>
+      </c>
+      <c r="G122" t="n">
         <v>2.7468</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>6.6415</v>
       </c>
     </row>
@@ -3985,9 +4353,12 @@
         <v>0.9623</v>
       </c>
       <c r="F123" t="n">
+        <v>1.4881</v>
+      </c>
+      <c r="G123" t="n">
         <v>3.3756</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>6.807</v>
       </c>
     </row>
@@ -4014,9 +4385,12 @@
         <v>0.9809</v>
       </c>
       <c r="F124" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="G124" t="n">
         <v>2.6421</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>6.6011</v>
       </c>
     </row>
@@ -4043,9 +4417,12 @@
         <v>0.9513</v>
       </c>
       <c r="F125" t="n">
+        <v>1.4909</v>
+      </c>
+      <c r="G125" t="n">
         <v>3.2415</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>6.8267</v>
       </c>
     </row>
@@ -4072,9 +4449,12 @@
         <v>0.9756</v>
       </c>
       <c r="F126" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="G126" t="n">
         <v>2.6694</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>7.2649</v>
       </c>
     </row>
@@ -4101,9 +4481,12 @@
         <v>0.9611</v>
       </c>
       <c r="F127" t="n">
+        <v>1.6464</v>
+      </c>
+      <c r="G127" t="n">
         <v>3.3133</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>7.8337</v>
       </c>
     </row>
@@ -4130,9 +4513,12 @@
         <v>0.9621</v>
       </c>
       <c r="F128" t="n">
+        <v>1.5545</v>
+      </c>
+      <c r="G128" t="n">
         <v>3.1482</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>7.2555</v>
       </c>
     </row>
@@ -4159,9 +4545,12 @@
         <v>0.9751</v>
       </c>
       <c r="F129" t="n">
+        <v>1.5572</v>
+      </c>
+      <c r="G129" t="n">
         <v>2.6851</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>7.2731</v>
       </c>
     </row>
@@ -4188,9 +4577,12 @@
         <v>0.9615</v>
       </c>
       <c r="F130" t="n">
+        <v>1.5543</v>
+      </c>
+      <c r="G130" t="n">
         <v>3.1615</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>7.2544</v>
       </c>
     </row>
@@ -4217,9 +4609,12 @@
         <v>0.9752999999999999</v>
       </c>
       <c r="F131" t="n">
+        <v>1.5575</v>
+      </c>
+      <c r="G131" t="n">
         <v>2.6649</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>7.2748</v>
       </c>
     </row>
@@ -4246,9 +4641,12 @@
         <v>0.9622000000000001</v>
       </c>
       <c r="F132" t="n">
+        <v>1.5551</v>
+      </c>
+      <c r="G132" t="n">
         <v>3.1391</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>7.2592</v>
       </c>
     </row>
@@ -4275,9 +4673,12 @@
         <v>0.9725</v>
       </c>
       <c r="F133" t="n">
+        <v>1.5569</v>
+      </c>
+      <c r="G133" t="n">
         <v>2.7032</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>7.2708</v>
       </c>
     </row>
@@ -4304,9 +4705,12 @@
         <v>0.9625</v>
       </c>
       <c r="F134" t="n">
+        <v>1.5594</v>
+      </c>
+      <c r="G134" t="n">
         <v>3.1368</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>7.2875</v>
       </c>
     </row>
@@ -4333,9 +4737,12 @@
         <v>0.9752999999999999</v>
       </c>
       <c r="F135" t="n">
+        <v>1.5582</v>
+      </c>
+      <c r="G135" t="n">
         <v>2.6687</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>7.2796</v>
       </c>
     </row>
@@ -4362,9 +4769,12 @@
         <v>0.9754</v>
       </c>
       <c r="F136" t="n">
+        <v>1.5595</v>
+      </c>
+      <c r="G136" t="n">
         <v>2.665</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>7.2883</v>
       </c>
     </row>
@@ -4391,9 +4801,12 @@
         <v>0.9702</v>
       </c>
       <c r="F137" t="n">
+        <v>1.4663</v>
+      </c>
+      <c r="G137" t="n">
         <v>2.7603</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>6.6531</v>
       </c>
     </row>
@@ -4420,9 +4833,12 @@
         <v>0.9727</v>
       </c>
       <c r="F138" t="n">
+        <v>1.4657</v>
+      </c>
+      <c r="G138" t="n">
         <v>2.6667</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>6.6494</v>
       </c>
     </row>
@@ -4449,9 +4865,12 @@
         <v>0.9712</v>
       </c>
       <c r="F139" t="n">
+        <v>1.4645</v>
+      </c>
+      <c r="G139" t="n">
         <v>2.7109</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>6.6404</v>
       </c>
     </row>
@@ -4478,9 +4897,12 @@
         <v>0.98</v>
       </c>
       <c r="F140" t="n">
+        <v>1.4324</v>
+      </c>
+      <c r="G140" t="n">
         <v>2.5053</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>6.4068</v>
       </c>
     </row>
@@ -4507,9 +4929,12 @@
         <v>0.9804</v>
       </c>
       <c r="F141" t="n">
+        <v>1.4371</v>
+      </c>
+      <c r="G141" t="n">
         <v>2.4246</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>6.4417</v>
       </c>
     </row>
@@ -4536,9 +4961,12 @@
         <v>0.9727</v>
       </c>
       <c r="F142" t="n">
+        <v>1.4657</v>
+      </c>
+      <c r="G142" t="n">
         <v>2.6667</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>6.6494</v>
       </c>
     </row>
@@ -4565,9 +4993,12 @@
         <v>0.9695</v>
       </c>
       <c r="F143" t="n">
+        <v>1.4771</v>
+      </c>
+      <c r="G143" t="n">
         <v>2.8022</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>6.7299</v>
       </c>
     </row>
@@ -4594,9 +5025,12 @@
         <v>0.9695</v>
       </c>
       <c r="F144" t="n">
+        <v>1.4782</v>
+      </c>
+      <c r="G144" t="n">
         <v>2.7974</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>6.738</v>
       </c>
     </row>
@@ -4623,9 +5057,12 @@
         <v>0.9804</v>
       </c>
       <c r="F145" t="n">
+        <v>1.4371</v>
+      </c>
+      <c r="G145" t="n">
         <v>2.4246</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>6.4417</v>
       </c>
     </row>
@@ -4652,9 +5089,12 @@
         <v>0.9588</v>
       </c>
       <c r="F146" t="n">
+        <v>1.654</v>
+      </c>
+      <c r="G146" t="n">
         <v>3.3838</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>7.8793</v>
       </c>
     </row>
@@ -4681,9 +5121,12 @@
         <v>0.9627</v>
       </c>
       <c r="F147" t="n">
+        <v>1.6614</v>
+      </c>
+      <c r="G147" t="n">
         <v>3.2902</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>7.9239</v>
       </c>
     </row>
@@ -4710,9 +5153,12 @@
         <v>0.9696</v>
       </c>
       <c r="F148" t="n">
+        <v>1.6575</v>
+      </c>
+      <c r="G148" t="n">
         <v>3.0505</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>7.9005</v>
       </c>
     </row>
@@ -4739,9 +5185,12 @@
         <v>0.9611</v>
       </c>
       <c r="F149" t="n">
+        <v>1.6565</v>
+      </c>
+      <c r="G149" t="n">
         <v>3.3181</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>7.8946</v>
       </c>
     </row>
@@ -4768,9 +5217,12 @@
         <v>0.9587</v>
       </c>
       <c r="F150" t="n">
+        <v>1.6475</v>
+      </c>
+      <c r="G150" t="n">
         <v>3.3786</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>7.8401</v>
       </c>
     </row>
@@ -4797,9 +5249,12 @@
         <v>0.9609</v>
       </c>
       <c r="F151" t="n">
+        <v>1.6468</v>
+      </c>
+      <c r="G151" t="n">
         <v>3.2998</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>7.8359</v>
       </c>
     </row>
@@ -4826,9 +5281,12 @@
         <v>0.9675</v>
       </c>
       <c r="F152" t="n">
+        <v>1.6431</v>
+      </c>
+      <c r="G152" t="n">
         <v>3.0747</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>7.8138</v>
       </c>
     </row>
@@ -4855,9 +5313,12 @@
         <v>0.9673</v>
       </c>
       <c r="F153" t="n">
+        <v>1.6435</v>
+      </c>
+      <c r="G153" t="n">
         <v>3.0973</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>7.8162</v>
       </c>
     </row>
@@ -4884,9 +5345,12 @@
         <v>0.9667</v>
       </c>
       <c r="F154" t="n">
+        <v>1.6467</v>
+      </c>
+      <c r="G154" t="n">
         <v>3.1162</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>7.8353</v>
       </c>
     </row>
@@ -4913,9 +5377,12 @@
         <v>0.9788</v>
       </c>
       <c r="F155" t="n">
+        <v>1.436</v>
+      </c>
+      <c r="G155" t="n">
         <v>2.5055</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>6.4333</v>
       </c>
     </row>
@@ -4942,9 +5409,12 @@
         <v>0.9812</v>
       </c>
       <c r="F156" t="n">
+        <v>1.4398</v>
+      </c>
+      <c r="G156" t="n">
         <v>2.4181</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>6.4617</v>
       </c>
     </row>
@@ -4971,9 +5441,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F157" t="n">
+        <v>1.4493</v>
+      </c>
+      <c r="G157" t="n">
         <v>2.583</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>6.5311</v>
       </c>
     </row>
@@ -5000,9 +5473,12 @@
         <v>0.982</v>
       </c>
       <c r="F158" t="n">
+        <v>1.3309</v>
+      </c>
+      <c r="G158" t="n">
         <v>2.205</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>5.6051</v>
       </c>
     </row>
@@ -5029,9 +5505,12 @@
         <v>0.967</v>
       </c>
       <c r="F159" t="n">
+        <v>1.5575</v>
+      </c>
+      <c r="G159" t="n">
         <v>2.9495</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>7.275</v>
       </c>
     </row>
@@ -5058,9 +5537,12 @@
         <v>0.9614</v>
       </c>
       <c r="F160" t="n">
+        <v>1.696</v>
+      </c>
+      <c r="G160" t="n">
         <v>3.4271</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>8.1286</v>
       </c>
     </row>
@@ -5087,9 +5569,12 @@
         <v>0.9537</v>
       </c>
       <c r="F161" t="n">
+        <v>1.6973</v>
+      </c>
+      <c r="G161" t="n">
         <v>3.7082</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>8.135899999999999</v>
       </c>
     </row>
@@ -5116,9 +5601,12 @@
         <v>0.9692</v>
       </c>
       <c r="F162" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="G162" t="n">
         <v>2.8768</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>7.2846</v>
       </c>
     </row>
@@ -5145,9 +5633,12 @@
         <v>0.9691</v>
       </c>
       <c r="F163" t="n">
+        <v>1.4812</v>
+      </c>
+      <c r="G163" t="n">
         <v>2.7986</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>6.7591</v>
       </c>
     </row>
@@ -5174,9 +5665,12 @@
         <v>0.9792999999999999</v>
       </c>
       <c r="F164" t="n">
+        <v>1.4319</v>
+      </c>
+      <c r="G164" t="n">
         <v>2.5516</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>6.403</v>
       </c>
     </row>
@@ -5203,9 +5697,12 @@
         <v>0.9513</v>
       </c>
       <c r="F165" t="n">
+        <v>1.4909</v>
+      </c>
+      <c r="G165" t="n">
         <v>3.2415</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>6.8267</v>
       </c>
     </row>
@@ -5232,9 +5729,12 @@
         <v>0.9147999999999999</v>
       </c>
       <c r="F166" t="n">
+        <v>1.5271</v>
+      </c>
+      <c r="G166" t="n">
         <v>4.1177</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>7.074</v>
       </c>
     </row>
@@ -5261,9 +5761,12 @@
         <v>0.9704</v>
       </c>
       <c r="F167" t="n">
+        <v>1.4545</v>
+      </c>
+      <c r="G167" t="n">
         <v>2.7079</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>6.5684</v>
       </c>
     </row>
@@ -5290,9 +5793,12 @@
         <v>0.9738</v>
       </c>
       <c r="F168" t="n">
+        <v>1.4844</v>
+      </c>
+      <c r="G168" t="n">
         <v>2.9207</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>6.7816</v>
       </c>
     </row>
@@ -5319,9 +5825,12 @@
         <v>0.9835</v>
       </c>
       <c r="F169" t="n">
+        <v>1.3722</v>
+      </c>
+      <c r="G169" t="n">
         <v>2.2512</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>5.9447</v>
       </c>
     </row>
@@ -5348,9 +5857,12 @@
         <v>0.9691</v>
       </c>
       <c r="F170" t="n">
+        <v>1.5478</v>
+      </c>
+      <c r="G170" t="n">
         <v>3.3713</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>7.2117</v>
       </c>
     </row>
@@ -5377,9 +5889,12 @@
         <v>0.9804</v>
       </c>
       <c r="F171" t="n">
+        <v>1.4734</v>
+      </c>
+      <c r="G171" t="n">
         <v>2.6953</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>6.7041</v>
       </c>
     </row>
@@ -5406,9 +5921,12 @@
         <v>0.9738</v>
       </c>
       <c r="F172" t="n">
+        <v>1.5204</v>
+      </c>
+      <c r="G172" t="n">
         <v>2.7303</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>7.029</v>
       </c>
     </row>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/eau/RANDOMSEARCH_DETAILS_eau.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/eau/RANDOMSEARCH_DETAILS_eau.xlsx
@@ -478,16 +478,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9849</v>
+        <v>0.9847</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3547</v>
+        <v>0.6168</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1723</v>
+        <v>2.1808</v>
       </c>
       <c r="H2" t="n">
-        <v>5.8032</v>
+        <v>5.8419</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9857</v>
+        <v>0.9853</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3352</v>
+        <v>0.6191</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0685</v>
+        <v>2.1964</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6412</v>
+        <v>5.8247</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.922</v>
+        <v>0.9577</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4899</v>
+        <v>0.4582</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9488</v>
+        <v>3.0015</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8195</v>
+        <v>6.9466</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9712</v>
+        <v>0.9403</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6505</v>
+        <v>0.2756</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8848</v>
+        <v>3.7801</v>
       </c>
       <c r="H5" t="n">
-        <v>7.8581</v>
+        <v>8.0322</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.9578</v>
+        <v>0.9361</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6633</v>
+        <v>0.2509</v>
       </c>
       <c r="G6" t="n">
-        <v>3.393</v>
+        <v>3.899</v>
       </c>
       <c r="H6" t="n">
-        <v>7.9352</v>
+        <v>8.168100000000001</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9717</v>
+        <v>0.9468</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5834</v>
+        <v>0.3226</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8433</v>
+        <v>3.6462</v>
       </c>
       <c r="H7" t="n">
-        <v>7.4422</v>
+        <v>7.7672</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9568</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5778</v>
+        <v>0.3655</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7956</v>
+        <v>3.2585</v>
       </c>
       <c r="H8" t="n">
-        <v>7.4061</v>
+        <v>7.5173</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9835</v>
+        <v>0.968</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4624</v>
+        <v>0.4894</v>
       </c>
       <c r="G9" t="n">
-        <v>2.344</v>
+        <v>3.1434</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6258</v>
+        <v>6.7438</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9728</v>
+        <v>0.9543</v>
       </c>
       <c r="F10" t="n">
-        <v>1.581</v>
+        <v>0.3613</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7799</v>
+        <v>3.3438</v>
       </c>
       <c r="H10" t="n">
-        <v>7.427</v>
+        <v>7.5422</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9618</v>
+        <v>0.9454</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5808</v>
+        <v>0.3614</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2396</v>
+        <v>3.5353</v>
       </c>
       <c r="H11" t="n">
-        <v>7.4257</v>
+        <v>7.5415</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9728</v>
+        <v>0.9474</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5848</v>
+        <v>0.3667</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7861</v>
+        <v>3.4835</v>
       </c>
       <c r="H12" t="n">
-        <v>7.4512</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9724</v>
+        <v>0.9484</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5848</v>
+        <v>0.3582</v>
       </c>
       <c r="G13" t="n">
-        <v>2.792</v>
+        <v>3.4834</v>
       </c>
       <c r="H13" t="n">
-        <v>7.4513</v>
+        <v>7.5602</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9728</v>
+        <v>0.9085</v>
       </c>
       <c r="F14" t="n">
-        <v>1.582</v>
+        <v>0.3538</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7905</v>
+        <v>4.3472</v>
       </c>
       <c r="H14" t="n">
-        <v>7.4331</v>
+        <v>7.5864</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9725</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5832</v>
+        <v>0.3628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7905</v>
+        <v>2.8935</v>
       </c>
       <c r="H15" t="n">
-        <v>7.4406</v>
+        <v>7.5332</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9724</v>
+        <v>0.9543</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5822</v>
+        <v>0.3647</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7983</v>
+        <v>3.3379</v>
       </c>
       <c r="H16" t="n">
-        <v>7.4343</v>
+        <v>7.5218</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9731</v>
+        <v>0.9559</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5796</v>
+        <v>0.3628</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7657</v>
+        <v>3.2992</v>
       </c>
       <c r="H17" t="n">
-        <v>7.4179</v>
+        <v>7.5334</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9735</v>
       </c>
       <c r="F18" t="n">
-        <v>1.458</v>
+        <v>0.4972</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4646</v>
+        <v>2.6793</v>
       </c>
       <c r="H18" t="n">
-        <v>6.5941</v>
+        <v>6.6918</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.97</v>
+        <v>0.9487</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4611</v>
+        <v>0.4733</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7406</v>
+        <v>3.4149</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6163</v>
+        <v>6.8493</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9714</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4761</v>
+        <v>0.4462</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7103</v>
+        <v>3.4929</v>
       </c>
       <c r="H20" t="n">
-        <v>6.7229</v>
+        <v>7.0229</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9684</v>
+        <v>0.9411</v>
       </c>
       <c r="F21" t="n">
-        <v>1.489</v>
+        <v>0.399</v>
       </c>
       <c r="G21" t="n">
-        <v>2.8653</v>
+        <v>3.6411</v>
       </c>
       <c r="H21" t="n">
-        <v>6.8132</v>
+        <v>7.3163</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9747</v>
+        <v>0.9096</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5005</v>
+        <v>0.3869</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6108</v>
+        <v>4.4427</v>
       </c>
       <c r="H22" t="n">
-        <v>6.8931</v>
+        <v>7.3894</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9729</v>
+        <v>0.9081</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5079</v>
+        <v>0.3807</v>
       </c>
       <c r="G23" t="n">
-        <v>2.6976</v>
+        <v>4.4609</v>
       </c>
       <c r="H23" t="n">
-        <v>6.9435</v>
+        <v>7.4264</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9648</v>
+        <v>0.9725</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5282</v>
+        <v>0.3804</v>
       </c>
       <c r="G24" t="n">
-        <v>3.0088</v>
+        <v>2.7688</v>
       </c>
       <c r="H24" t="n">
-        <v>7.0814</v>
+        <v>7.4284</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9611</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>1.534</v>
+        <v>0.3833</v>
       </c>
       <c r="G25" t="n">
-        <v>3.1526</v>
+        <v>4.7226</v>
       </c>
       <c r="H25" t="n">
-        <v>7.1203</v>
+        <v>7.4111</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9758</v>
+        <v>0.9601</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4604</v>
+        <v>0.5062</v>
       </c>
       <c r="G26" t="n">
-        <v>2.5894</v>
+        <v>3.1974</v>
       </c>
       <c r="H26" t="n">
-        <v>6.611</v>
+        <v>6.6315</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9742</v>
+        <v>0.9764</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4559</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>2.6873</v>
+        <v>2.5929</v>
       </c>
       <c r="H27" t="n">
-        <v>6.5785</v>
+        <v>6.5955</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9758</v>
+        <v>0.9556</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4508</v>
+        <v>0.5141</v>
       </c>
       <c r="G28" t="n">
-        <v>2.6004</v>
+        <v>3.279</v>
       </c>
       <c r="H28" t="n">
-        <v>6.5423</v>
+        <v>6.5784</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9742</v>
+        <v>0.9493</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4566</v>
+        <v>0.4724</v>
       </c>
       <c r="G29" t="n">
-        <v>2.6156</v>
+        <v>3.4335</v>
       </c>
       <c r="H29" t="n">
-        <v>6.5838</v>
+        <v>6.8549</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9722</v>
+        <v>0.9456</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4708</v>
+        <v>0.4459</v>
       </c>
       <c r="G30" t="n">
-        <v>2.7233</v>
+        <v>3.5021</v>
       </c>
       <c r="H30" t="n">
-        <v>6.6851</v>
+        <v>7.0251</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9752</v>
+        <v>0.9472</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4782</v>
+        <v>0.4053</v>
       </c>
       <c r="G31" t="n">
-        <v>2.5863</v>
+        <v>3.473</v>
       </c>
       <c r="H31" t="n">
-        <v>6.7375</v>
+        <v>7.2779</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9661</v>
+        <v>0.9111</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4989</v>
+        <v>0.3869</v>
       </c>
       <c r="G32" t="n">
-        <v>2.9307</v>
+        <v>4.4333</v>
       </c>
       <c r="H32" t="n">
-        <v>6.8819</v>
+        <v>7.3893</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9736</v>
+        <v>0.912</v>
       </c>
       <c r="F33" t="n">
-        <v>1.5049</v>
+        <v>0.3867</v>
       </c>
       <c r="G33" t="n">
-        <v>2.6523</v>
+        <v>4.4035</v>
       </c>
       <c r="H33" t="n">
-        <v>6.923</v>
+        <v>7.3907</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9779</v>
+        <v>0.9633</v>
       </c>
       <c r="F34" t="n">
-        <v>1.4885</v>
+        <v>0.4651</v>
       </c>
       <c r="G34" t="n">
-        <v>2.8199</v>
+        <v>3.2892</v>
       </c>
       <c r="H34" t="n">
-        <v>6.8102</v>
+        <v>6.9021</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9629</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4789</v>
+        <v>0.4904</v>
       </c>
       <c r="G35" t="n">
-        <v>3.2711</v>
+        <v>2.5277</v>
       </c>
       <c r="H35" t="n">
-        <v>6.7429</v>
+        <v>6.7368</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9846</v>
+        <v>0.982</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4643</v>
+        <v>0.5178</v>
       </c>
       <c r="G36" t="n">
-        <v>2.4375</v>
+        <v>2.5473</v>
       </c>
       <c r="H36" t="n">
-        <v>6.6389</v>
+        <v>6.5531</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.984</v>
+        <v>0.9805</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4783</v>
+        <v>0.5059</v>
       </c>
       <c r="G37" t="n">
-        <v>2.4229</v>
+        <v>2.6347</v>
       </c>
       <c r="H37" t="n">
-        <v>6.7388</v>
+        <v>6.6335</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9767</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>1.4666</v>
+        <v>0.4992</v>
       </c>
       <c r="G38" t="n">
-        <v>2.7033</v>
+        <v>2.3409</v>
       </c>
       <c r="H38" t="n">
-        <v>6.6555</v>
+        <v>6.6782</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9843</v>
+        <v>0.9796</v>
       </c>
       <c r="F39" t="n">
-        <v>1.4809</v>
+        <v>0.5112</v>
       </c>
       <c r="G39" t="n">
-        <v>2.4231</v>
+        <v>2.6999</v>
       </c>
       <c r="H39" t="n">
-        <v>6.7567</v>
+        <v>6.5979</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9775</v>
+        <v>0.9784</v>
       </c>
       <c r="F40" t="n">
-        <v>1.4859</v>
+        <v>0.4893</v>
       </c>
       <c r="G40" t="n">
-        <v>2.703</v>
+        <v>2.7374</v>
       </c>
       <c r="H40" t="n">
-        <v>6.7916</v>
+        <v>6.7445</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9644</v>
+        <v>0.9634</v>
       </c>
       <c r="F41" t="n">
-        <v>1.4895</v>
+        <v>0.4656</v>
       </c>
       <c r="G41" t="n">
-        <v>3.2334</v>
+        <v>3.2867</v>
       </c>
       <c r="H41" t="n">
-        <v>6.8171</v>
+        <v>6.8991</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9627</v>
+        <v>0.9821</v>
       </c>
       <c r="F42" t="n">
-        <v>1.4783</v>
+        <v>0.4843</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2728</v>
+        <v>2.5343</v>
       </c>
       <c r="H42" t="n">
-        <v>6.7383</v>
+        <v>6.7771</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9813</v>
+        <v>0.9839</v>
       </c>
       <c r="F43" t="n">
-        <v>1.4643</v>
+        <v>0.5175</v>
       </c>
       <c r="G43" t="n">
-        <v>2.5948</v>
+        <v>2.4153</v>
       </c>
       <c r="H43" t="n">
-        <v>6.6395</v>
+        <v>6.5551</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.985</v>
+        <v>0.9805</v>
       </c>
       <c r="F44" t="n">
-        <v>1.4805</v>
+        <v>0.5077</v>
       </c>
       <c r="G44" t="n">
-        <v>2.3958</v>
+        <v>2.6324</v>
       </c>
       <c r="H44" t="n">
-        <v>6.7537</v>
+        <v>6.6213</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9768</v>
+        <v>0.9871</v>
       </c>
       <c r="F45" t="n">
-        <v>1.4697</v>
+        <v>0.4989</v>
       </c>
       <c r="G45" t="n">
-        <v>2.7082</v>
+        <v>2.3463</v>
       </c>
       <c r="H45" t="n">
-        <v>6.6776</v>
+        <v>6.6807</v>
       </c>
     </row>
     <row r="46">
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9782</v>
+        <v>0.9799</v>
       </c>
       <c r="F46" t="n">
-        <v>1.4867</v>
+        <v>0.5034</v>
       </c>
       <c r="G46" t="n">
-        <v>2.6999</v>
+        <v>2.6902</v>
       </c>
       <c r="H46" t="n">
-        <v>6.7973</v>
+        <v>6.6505</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9781</v>
+        <v>0.9786</v>
       </c>
       <c r="F47" t="n">
-        <v>1.4858</v>
+        <v>0.4851</v>
       </c>
       <c r="G47" t="n">
-        <v>2.6879</v>
+        <v>2.7273</v>
       </c>
       <c r="H47" t="n">
-        <v>6.7913</v>
+        <v>6.7721</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9862</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>1.4668</v>
+        <v>0.5544</v>
       </c>
       <c r="G48" t="n">
-        <v>2.4051</v>
+        <v>2.4148</v>
       </c>
       <c r="H48" t="n">
-        <v>6.6567</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.982</v>
       </c>
       <c r="F49" t="n">
-        <v>1.4542</v>
+        <v>0.5175</v>
       </c>
       <c r="G49" t="n">
-        <v>2.5386</v>
+        <v>2.5803</v>
       </c>
       <c r="H49" t="n">
-        <v>6.5669</v>
+        <v>6.5555</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9841</v>
+        <v>0.9805</v>
       </c>
       <c r="F50" t="n">
-        <v>1.3279</v>
+        <v>0.6332</v>
       </c>
       <c r="G50" t="n">
-        <v>2.0631</v>
+        <v>2.2722</v>
       </c>
       <c r="H50" t="n">
-        <v>5.5792</v>
+        <v>5.7159</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.9747</v>
+        <v>0.9697</v>
       </c>
       <c r="F51" t="n">
-        <v>1.5343</v>
+        <v>0.3753</v>
       </c>
       <c r="G51" t="n">
-        <v>2.9004</v>
+        <v>3.0903</v>
       </c>
       <c r="H51" t="n">
-        <v>7.1222</v>
+        <v>7.4591</v>
       </c>
     </row>
     <row r="52">
@@ -2078,16 +2078,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9742</v>
+        <v>0.9695</v>
       </c>
       <c r="F52" t="n">
-        <v>1.5552</v>
+        <v>0.3571</v>
       </c>
       <c r="G52" t="n">
-        <v>2.928</v>
+        <v>3.1215</v>
       </c>
       <c r="H52" t="n">
-        <v>7.26</v>
+        <v>7.5669</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9831</v>
+        <v>0.9722</v>
       </c>
       <c r="F53" t="n">
-        <v>1.4893</v>
+        <v>0.447</v>
       </c>
       <c r="G53" t="n">
-        <v>2.4269</v>
+        <v>2.9725</v>
       </c>
       <c r="H53" t="n">
-        <v>6.8156</v>
+        <v>7.018</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9756</v>
+        <v>0.966</v>
       </c>
       <c r="F54" t="n">
-        <v>1.5095</v>
+        <v>0.3805</v>
       </c>
       <c r="G54" t="n">
-        <v>2.7161</v>
+        <v>3.1214</v>
       </c>
       <c r="H54" t="n">
-        <v>6.955</v>
+        <v>7.4282</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.984</v>
+        <v>0.9802</v>
       </c>
       <c r="F55" t="n">
-        <v>1.3818</v>
+        <v>0.5706</v>
       </c>
       <c r="G55" t="n">
-        <v>2.1524</v>
+        <v>2.3638</v>
       </c>
       <c r="H55" t="n">
-        <v>6.0202</v>
+        <v>6.1838</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9829</v>
+        <v>0.9822</v>
       </c>
       <c r="F56" t="n">
-        <v>1.3469</v>
+        <v>0.6139</v>
       </c>
       <c r="G56" t="n">
-        <v>2.2143</v>
+        <v>2.2934</v>
       </c>
       <c r="H56" t="n">
-        <v>5.739</v>
+        <v>5.8638</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9842</v>
+        <v>0.97</v>
       </c>
       <c r="F57" t="n">
-        <v>1.3177</v>
+        <v>0.6502</v>
       </c>
       <c r="G57" t="n">
-        <v>2.1137</v>
+        <v>2.7402</v>
       </c>
       <c r="H57" t="n">
-        <v>5.4916</v>
+        <v>5.5817</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>1.6701</v>
+        <v>0.2502</v>
       </c>
       <c r="G58" t="n">
-        <v>3.3829</v>
+        <v>3.9268</v>
       </c>
       <c r="H58" t="n">
-        <v>7.9759</v>
+        <v>8.1717</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.9589</v>
+        <v>0.9475</v>
       </c>
       <c r="F59" t="n">
-        <v>1.6693</v>
+        <v>0.244</v>
       </c>
       <c r="G59" t="n">
-        <v>3.3735</v>
+        <v>3.6085</v>
       </c>
       <c r="H59" t="n">
-        <v>7.9709</v>
+        <v>8.2058</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.958</v>
+        <v>0.9467</v>
       </c>
       <c r="F60" t="n">
-        <v>1.6701</v>
+        <v>0.2436</v>
       </c>
       <c r="G60" t="n">
-        <v>3.3885</v>
+        <v>3.6216</v>
       </c>
       <c r="H60" t="n">
-        <v>7.9761</v>
+        <v>8.2079</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9566</v>
+        <v>0.9478</v>
       </c>
       <c r="F61" t="n">
-        <v>1.6774</v>
+        <v>0.2474</v>
       </c>
       <c r="G61" t="n">
-        <v>3.412</v>
+        <v>3.5721</v>
       </c>
       <c r="H61" t="n">
-        <v>8.0192</v>
+        <v>8.1868</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9792</v>
+        <v>0.9749</v>
       </c>
       <c r="F62" t="n">
-        <v>1.3816</v>
+        <v>0.5584</v>
       </c>
       <c r="G62" t="n">
-        <v>2.4255</v>
+        <v>2.6183</v>
       </c>
       <c r="H62" t="n">
-        <v>6.0189</v>
+        <v>6.2712</v>
       </c>
     </row>
     <row r="63">
@@ -2430,16 +2430,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.978</v>
+        <v>0.9786</v>
       </c>
       <c r="F63" t="n">
-        <v>1.3903</v>
+        <v>0.5525</v>
       </c>
       <c r="G63" t="n">
-        <v>2.4553</v>
+        <v>2.478</v>
       </c>
       <c r="H63" t="n">
-        <v>6.0868</v>
+        <v>6.3132</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9772</v>
+        <v>0.9775</v>
       </c>
       <c r="F64" t="n">
-        <v>1.3964</v>
+        <v>0.5535</v>
       </c>
       <c r="G64" t="n">
-        <v>2.5117</v>
+        <v>2.5082</v>
       </c>
       <c r="H64" t="n">
-        <v>6.1346</v>
+        <v>6.3059</v>
       </c>
     </row>
     <row r="65">
@@ -2494,16 +2494,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.98</v>
+        <v>0.9795</v>
       </c>
       <c r="F65" t="n">
-        <v>1.4007</v>
+        <v>0.5552</v>
       </c>
       <c r="G65" t="n">
-        <v>2.2955</v>
+        <v>2.3304</v>
       </c>
       <c r="H65" t="n">
-        <v>6.1676</v>
+        <v>6.2937</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9853</v>
+        <v>0.9822</v>
       </c>
       <c r="F66" t="n">
-        <v>1.3098</v>
+        <v>0.6434</v>
       </c>
       <c r="G66" t="n">
-        <v>1.9944</v>
+        <v>2.1793</v>
       </c>
       <c r="H66" t="n">
-        <v>5.4229</v>
+        <v>5.6356</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9833</v>
+        <v>0.9684</v>
       </c>
       <c r="F67" t="n">
-        <v>1.3269</v>
+        <v>0.6438</v>
       </c>
       <c r="G67" t="n">
-        <v>2.1416</v>
+        <v>2.8027</v>
       </c>
       <c r="H67" t="n">
-        <v>5.5704</v>
+        <v>5.6323</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9825</v>
+        <v>0.9817</v>
       </c>
       <c r="F68" t="n">
-        <v>1.3278</v>
+        <v>0.6339</v>
       </c>
       <c r="G68" t="n">
-        <v>2.156</v>
+        <v>2.2306</v>
       </c>
       <c r="H68" t="n">
-        <v>5.5785</v>
+        <v>5.7098</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9726</v>
+        <v>0.9729</v>
       </c>
       <c r="F69" t="n">
-        <v>1.4504</v>
+        <v>0.5079</v>
       </c>
       <c r="G69" t="n">
-        <v>2.7223</v>
+        <v>2.6398</v>
       </c>
       <c r="H69" t="n">
-        <v>6.539</v>
+        <v>6.6201</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9725</v>
       </c>
       <c r="F70" t="n">
-        <v>1.454</v>
+        <v>0.531</v>
       </c>
       <c r="G70" t="n">
-        <v>2.8527</v>
+        <v>2.6072</v>
       </c>
       <c r="H70" t="n">
-        <v>6.5651</v>
+        <v>6.4629</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9748</v>
+        <v>0.9497</v>
       </c>
       <c r="F71" t="n">
-        <v>1.4288</v>
+        <v>0.5039</v>
       </c>
       <c r="G71" t="n">
-        <v>2.6176</v>
+        <v>3.3754</v>
       </c>
       <c r="H71" t="n">
-        <v>6.3804</v>
+        <v>6.6468</v>
       </c>
     </row>
     <row r="72">
@@ -2718,16 +2718,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9738</v>
+        <v>0.9735</v>
       </c>
       <c r="F72" t="n">
-        <v>1.4371</v>
+        <v>0.5236</v>
       </c>
       <c r="G72" t="n">
-        <v>2.6509</v>
+        <v>2.5974</v>
       </c>
       <c r="H72" t="n">
-        <v>6.4414</v>
+        <v>6.5135</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9784</v>
+        <v>0.9771</v>
       </c>
       <c r="F73" t="n">
-        <v>1.5551</v>
+        <v>0.4254</v>
       </c>
       <c r="G73" t="n">
-        <v>2.9238</v>
+        <v>2.9389</v>
       </c>
       <c r="H73" t="n">
-        <v>7.2592</v>
+        <v>7.154</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9782</v>
+        <v>0.9741</v>
       </c>
       <c r="F74" t="n">
-        <v>1.5949</v>
+        <v>0.4196</v>
       </c>
       <c r="G74" t="n">
-        <v>2.9899</v>
+        <v>3.1575</v>
       </c>
       <c r="H74" t="n">
-        <v>7.5148</v>
+        <v>7.1897</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9103</v>
       </c>
       <c r="F75" t="n">
-        <v>1.6108</v>
+        <v>0.3293</v>
       </c>
       <c r="G75" t="n">
-        <v>3.6706</v>
+        <v>4.35</v>
       </c>
       <c r="H75" t="n">
-        <v>7.6149</v>
+        <v>7.7286</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9103</v>
       </c>
       <c r="F76" t="n">
-        <v>1.6108</v>
+        <v>0.3293</v>
       </c>
       <c r="G76" t="n">
-        <v>3.6706</v>
+        <v>4.35</v>
       </c>
       <c r="H76" t="n">
-        <v>7.6149</v>
+        <v>7.7286</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9359</v>
       </c>
       <c r="F77" t="n">
-        <v>1.688</v>
+        <v>0.2282</v>
       </c>
       <c r="G77" t="n">
-        <v>2.9525</v>
+        <v>3.9732</v>
       </c>
       <c r="H77" t="n">
-        <v>8.0817</v>
+        <v>8.290699999999999</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9621</v>
+        <v>0.9364</v>
       </c>
       <c r="F78" t="n">
-        <v>1.6858</v>
+        <v>0.2345</v>
       </c>
       <c r="G78" t="n">
-        <v>3.2336</v>
+        <v>3.9797</v>
       </c>
       <c r="H78" t="n">
-        <v>8.068899999999999</v>
+        <v>8.257099999999999</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.9611</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F79" t="n">
-        <v>1.6826</v>
+        <v>0.2287</v>
       </c>
       <c r="G79" t="n">
-        <v>3.3536</v>
+        <v>3.9983</v>
       </c>
       <c r="H79" t="n">
-        <v>8.0502</v>
+        <v>8.2881</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.97</v>
+        <v>0.9362</v>
       </c>
       <c r="F80" t="n">
-        <v>1.6868</v>
+        <v>0.2336</v>
       </c>
       <c r="G80" t="n">
-        <v>2.9679</v>
+        <v>3.982</v>
       </c>
       <c r="H80" t="n">
-        <v>8.074999999999999</v>
+        <v>8.261799999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3006,16 +3006,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9829</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F81" t="n">
-        <v>1.3504</v>
+        <v>0.6088</v>
       </c>
       <c r="G81" t="n">
-        <v>2.1298</v>
+        <v>2.1778</v>
       </c>
       <c r="H81" t="n">
-        <v>5.7675</v>
+        <v>5.9023</v>
       </c>
     </row>
     <row r="82">
@@ -3038,16 +3038,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.982</v>
+        <v>0.9821</v>
       </c>
       <c r="F82" t="n">
-        <v>1.3583</v>
+        <v>0.6021</v>
       </c>
       <c r="G82" t="n">
-        <v>2.1805</v>
+        <v>2.2098</v>
       </c>
       <c r="H82" t="n">
-        <v>5.8321</v>
+        <v>5.9532</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9073</v>
       </c>
       <c r="F83" t="n">
-        <v>1.6012</v>
+        <v>0.315</v>
       </c>
       <c r="G83" t="n">
-        <v>3.0943</v>
+        <v>4.4031</v>
       </c>
       <c r="H83" t="n">
-        <v>7.5546</v>
+        <v>7.8108</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9482</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="F84" t="n">
-        <v>1.6072</v>
+        <v>0.314</v>
       </c>
       <c r="G84" t="n">
-        <v>3.6807</v>
+        <v>4.4047</v>
       </c>
       <c r="H84" t="n">
-        <v>7.5922</v>
+        <v>7.8167</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9678</v>
+        <v>0.9081</v>
       </c>
       <c r="F85" t="n">
-        <v>1.6044</v>
+        <v>0.3194</v>
       </c>
       <c r="G85" t="n">
-        <v>3.092</v>
+        <v>4.3912</v>
       </c>
       <c r="H85" t="n">
-        <v>7.5748</v>
+        <v>7.7857</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9761</v>
+        <v>0.9574</v>
       </c>
       <c r="F86" t="n">
-        <v>1.4595</v>
+        <v>0.4846</v>
       </c>
       <c r="G86" t="n">
-        <v>2.6047</v>
+        <v>3.258</v>
       </c>
       <c r="H86" t="n">
-        <v>6.6044</v>
+        <v>6.7754</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9754</v>
+        <v>0.9556</v>
       </c>
       <c r="F87" t="n">
-        <v>1.4548</v>
+        <v>0.4773</v>
       </c>
       <c r="G87" t="n">
-        <v>2.5908</v>
+        <v>3.2933</v>
       </c>
       <c r="H87" t="n">
-        <v>6.5708</v>
+        <v>6.8229</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9737</v>
+        <v>0.9735</v>
       </c>
       <c r="F88" t="n">
-        <v>1.4482</v>
+        <v>0.5014</v>
       </c>
       <c r="G88" t="n">
-        <v>2.6315</v>
+        <v>2.654</v>
       </c>
       <c r="H88" t="n">
-        <v>6.5228</v>
+        <v>6.664</v>
       </c>
     </row>
     <row r="89">
@@ -3262,16 +3262,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9748</v>
+        <v>0.9735</v>
       </c>
       <c r="F89" t="n">
-        <v>1.4634</v>
+        <v>0.514</v>
       </c>
       <c r="G89" t="n">
-        <v>2.6146</v>
+        <v>2.6515</v>
       </c>
       <c r="H89" t="n">
-        <v>6.6326</v>
+        <v>6.5788</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9812</v>
+        <v>0.9821</v>
       </c>
       <c r="F90" t="n">
-        <v>1.4646</v>
+        <v>0.5167</v>
       </c>
       <c r="G90" t="n">
-        <v>2.5971</v>
+        <v>2.5335</v>
       </c>
       <c r="H90" t="n">
-        <v>6.6414</v>
+        <v>6.5608</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.985</v>
+        <v>0.9805</v>
       </c>
       <c r="F91" t="n">
-        <v>1.4805</v>
+        <v>0.5078</v>
       </c>
       <c r="G91" t="n">
-        <v>2.3984</v>
+        <v>2.6327</v>
       </c>
       <c r="H91" t="n">
-        <v>6.7543</v>
+        <v>6.6209</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9737</v>
+        <v>0.9735</v>
       </c>
       <c r="F92" t="n">
-        <v>1.4482</v>
+        <v>0.5014</v>
       </c>
       <c r="G92" t="n">
-        <v>2.6315</v>
+        <v>2.654</v>
       </c>
       <c r="H92" t="n">
-        <v>6.5228</v>
+        <v>6.664</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.985</v>
+        <v>0.9805</v>
       </c>
       <c r="F93" t="n">
-        <v>1.4805</v>
+        <v>0.5078</v>
       </c>
       <c r="G93" t="n">
-        <v>2.3984</v>
+        <v>2.6327</v>
       </c>
       <c r="H93" t="n">
-        <v>6.7543</v>
+        <v>6.6209</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.922</v>
+        <v>0.9577</v>
       </c>
       <c r="F94" t="n">
-        <v>1.4899</v>
+        <v>0.4582</v>
       </c>
       <c r="G94" t="n">
-        <v>3.9488</v>
+        <v>3.0015</v>
       </c>
       <c r="H94" t="n">
-        <v>6.8195</v>
+        <v>6.9466</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.9407</v>
+        <v>0.9496</v>
       </c>
       <c r="F95" t="n">
-        <v>1.5222</v>
+        <v>0.4296</v>
       </c>
       <c r="G95" t="n">
-        <v>3.5304</v>
+        <v>3.1667</v>
       </c>
       <c r="H95" t="n">
-        <v>7.041</v>
+        <v>7.1277</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9214</v>
+        <v>0.957</v>
       </c>
       <c r="F96" t="n">
-        <v>1.4886</v>
+        <v>0.4625</v>
       </c>
       <c r="G96" t="n">
-        <v>3.9606</v>
+        <v>2.9855</v>
       </c>
       <c r="H96" t="n">
-        <v>6.8107</v>
+        <v>6.9188</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9566</v>
       </c>
       <c r="F97" t="n">
-        <v>1.4894</v>
+        <v>0.4587</v>
       </c>
       <c r="G97" t="n">
-        <v>3.972</v>
+        <v>3.0044</v>
       </c>
       <c r="H97" t="n">
-        <v>6.816</v>
+        <v>6.9432</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9764</v>
+        <v>0.9785</v>
       </c>
       <c r="F98" t="n">
-        <v>1.4457</v>
+        <v>0.5573</v>
       </c>
       <c r="G98" t="n">
-        <v>2.6991</v>
+        <v>2.5563</v>
       </c>
       <c r="H98" t="n">
-        <v>6.5046</v>
+        <v>6.2791</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9776</v>
+        <v>0.9739</v>
       </c>
       <c r="F99" t="n">
-        <v>1.4548</v>
+        <v>0.5369</v>
       </c>
       <c r="G99" t="n">
-        <v>2.6033</v>
+        <v>2.7251</v>
       </c>
       <c r="H99" t="n">
-        <v>6.571</v>
+        <v>6.4219</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9746</v>
+        <v>0.9726</v>
       </c>
       <c r="F100" t="n">
-        <v>1.4672</v>
+        <v>0.5281</v>
       </c>
       <c r="G100" t="n">
-        <v>2.7024</v>
+        <v>2.7629</v>
       </c>
       <c r="H100" t="n">
-        <v>6.6596</v>
+        <v>6.4831</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.982</v>
+        <v>0.9732</v>
       </c>
       <c r="F101" t="n">
-        <v>1.4738</v>
+        <v>0.5228</v>
       </c>
       <c r="G101" t="n">
-        <v>2.3796</v>
+        <v>2.717</v>
       </c>
       <c r="H101" t="n">
-        <v>6.7068</v>
+        <v>6.5192</v>
       </c>
     </row>
     <row r="102">
@@ -3678,16 +3678,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F102" t="n">
-        <v>1.4739</v>
+        <v>0.5251</v>
       </c>
       <c r="G102" t="n">
-        <v>2.628</v>
+        <v>2.5306</v>
       </c>
       <c r="H102" t="n">
-        <v>6.7076</v>
+        <v>6.5036</v>
       </c>
     </row>
     <row r="103">
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.978</v>
+        <v>0.9767</v>
       </c>
       <c r="F103" t="n">
-        <v>1.4945</v>
+        <v>0.5128</v>
       </c>
       <c r="G103" t="n">
-        <v>2.733</v>
+        <v>2.6885</v>
       </c>
       <c r="H103" t="n">
-        <v>6.8517</v>
+        <v>6.5872</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.978</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="F104" t="n">
-        <v>1.4461</v>
+        <v>0.5594</v>
       </c>
       <c r="G104" t="n">
-        <v>2.6357</v>
+        <v>2.4725</v>
       </c>
       <c r="H104" t="n">
-        <v>6.5076</v>
+        <v>6.264</v>
       </c>
     </row>
     <row r="105">
@@ -3774,16 +3774,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9766</v>
+        <v>0.9772</v>
       </c>
       <c r="F105" t="n">
-        <v>1.4529</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="G105" t="n">
-        <v>2.6562</v>
+        <v>2.5855</v>
       </c>
       <c r="H105" t="n">
-        <v>6.5572</v>
+        <v>6.3317</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9776</v>
+        <v>0.976</v>
       </c>
       <c r="F106" t="n">
-        <v>1.4534</v>
+        <v>0.5356</v>
       </c>
       <c r="G106" t="n">
-        <v>2.5694</v>
+        <v>2.6374</v>
       </c>
       <c r="H106" t="n">
-        <v>6.5608</v>
+        <v>6.4314</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9724</v>
+        <v>0.9827</v>
       </c>
       <c r="F107" t="n">
-        <v>1.4705</v>
+        <v>0.5261</v>
       </c>
       <c r="G107" t="n">
-        <v>2.7994</v>
+        <v>2.36</v>
       </c>
       <c r="H107" t="n">
-        <v>6.6836</v>
+        <v>6.4963</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9796</v>
+        <v>0.9799</v>
       </c>
       <c r="F108" t="n">
-        <v>1.5402</v>
+        <v>0.4964</v>
       </c>
       <c r="G108" t="n">
-        <v>2.7218</v>
+        <v>2.7465</v>
       </c>
       <c r="H108" t="n">
-        <v>7.1614</v>
+        <v>6.697</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9806</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>1.4887</v>
+        <v>0.5255</v>
       </c>
       <c r="G109" t="n">
-        <v>2.6966</v>
+        <v>2.7656</v>
       </c>
       <c r="H109" t="n">
-        <v>6.8116</v>
+        <v>6.5009</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9805</v>
+        <v>0.9745</v>
       </c>
       <c r="F110" t="n">
-        <v>1.4454</v>
+        <v>0.541</v>
       </c>
       <c r="G110" t="n">
-        <v>2.5965</v>
+        <v>2.7231</v>
       </c>
       <c r="H110" t="n">
-        <v>6.5024</v>
+        <v>6.3939</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9768</v>
+        <v>0.9529</v>
       </c>
       <c r="F111" t="n">
-        <v>1.4397</v>
+        <v>0.5295</v>
       </c>
       <c r="G111" t="n">
-        <v>2.6509</v>
+        <v>3.3634</v>
       </c>
       <c r="H111" t="n">
-        <v>6.4606</v>
+        <v>6.4735</v>
       </c>
     </row>
     <row r="112">
@@ -3998,16 +3998,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9795</v>
+        <v>0.9801</v>
       </c>
       <c r="F112" t="n">
-        <v>1.5396</v>
+        <v>0.4967</v>
       </c>
       <c r="G112" t="n">
-        <v>2.8263</v>
+        <v>2.7412</v>
       </c>
       <c r="H112" t="n">
-        <v>7.1571</v>
+        <v>6.6952</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9621</v>
+        <v>0.9772</v>
       </c>
       <c r="F113" t="n">
-        <v>1.4889</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>3.3734</v>
+        <v>2.7769</v>
       </c>
       <c r="H113" t="n">
-        <v>6.8124</v>
+        <v>6.5266</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9804</v>
+        <v>0.9738</v>
       </c>
       <c r="F114" t="n">
-        <v>1.4505</v>
+        <v>0.5387</v>
       </c>
       <c r="G114" t="n">
-        <v>2.6002</v>
+        <v>2.7544</v>
       </c>
       <c r="H114" t="n">
-        <v>6.5395</v>
+        <v>6.4096</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.9758</v>
       </c>
       <c r="F115" t="n">
-        <v>1.4319</v>
+        <v>0.536</v>
       </c>
       <c r="G115" t="n">
-        <v>2.7357</v>
+        <v>2.5972</v>
       </c>
       <c r="H115" t="n">
-        <v>6.4034</v>
+        <v>6.4287</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9697</v>
+        <v>0.9737</v>
       </c>
       <c r="F116" t="n">
-        <v>1.3955</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="G116" t="n">
-        <v>2.666</v>
+        <v>2.5279</v>
       </c>
       <c r="H116" t="n">
-        <v>6.1272</v>
+        <v>6.4298</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9731</v>
+        <v>0.9771</v>
       </c>
       <c r="F117" t="n">
-        <v>1.4014</v>
+        <v>0.5334</v>
       </c>
       <c r="G117" t="n">
-        <v>2.5903</v>
+        <v>2.3468</v>
       </c>
       <c r="H117" t="n">
-        <v>6.1732</v>
+        <v>6.4462</v>
       </c>
     </row>
     <row r="118">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9766</v>
+        <v>0.9772</v>
       </c>
       <c r="F118" t="n">
-        <v>1.4529</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="G118" t="n">
-        <v>2.6562</v>
+        <v>2.5855</v>
       </c>
       <c r="H118" t="n">
-        <v>6.5572</v>
+        <v>6.3317</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9621</v>
+        <v>0.9772</v>
       </c>
       <c r="F119" t="n">
-        <v>1.4889</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G119" t="n">
-        <v>3.3734</v>
+        <v>2.7769</v>
       </c>
       <c r="H119" t="n">
-        <v>6.8124</v>
+        <v>6.5266</v>
       </c>
     </row>
     <row r="120">
@@ -4254,16 +4254,16 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9626</v>
+        <v>0.9584</v>
       </c>
       <c r="F120" t="n">
-        <v>1.6032</v>
+        <v>0.4519</v>
       </c>
       <c r="G120" t="n">
-        <v>3.1486</v>
+        <v>3.1199</v>
       </c>
       <c r="H120" t="n">
-        <v>7.5671</v>
+        <v>6.9866</v>
       </c>
     </row>
     <row r="121">
@@ -4286,16 +4286,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9626</v>
+        <v>0.9584</v>
       </c>
       <c r="F121" t="n">
-        <v>1.6032</v>
+        <v>0.4519</v>
       </c>
       <c r="G121" t="n">
-        <v>3.1486</v>
+        <v>3.1199</v>
       </c>
       <c r="H121" t="n">
-        <v>7.5671</v>
+        <v>6.9866</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9689</v>
+        <v>0.9585</v>
       </c>
       <c r="F122" t="n">
-        <v>1.4646</v>
+        <v>0.5144</v>
       </c>
       <c r="G122" t="n">
-        <v>2.7468</v>
+        <v>3.0013</v>
       </c>
       <c r="H122" t="n">
-        <v>6.6415</v>
+        <v>6.5765</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9623</v>
+        <v>0.9771</v>
       </c>
       <c r="F123" t="n">
-        <v>1.4881</v>
+        <v>0.5182</v>
       </c>
       <c r="G123" t="n">
-        <v>3.3756</v>
+        <v>2.7799</v>
       </c>
       <c r="H123" t="n">
-        <v>6.807</v>
+        <v>6.5504</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9809</v>
+        <v>0.9781</v>
       </c>
       <c r="F124" t="n">
-        <v>1.459</v>
+        <v>0.5285</v>
       </c>
       <c r="G124" t="n">
-        <v>2.6421</v>
+        <v>2.6806</v>
       </c>
       <c r="H124" t="n">
-        <v>6.6011</v>
+        <v>6.4799</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9513</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>1.4909</v>
+        <v>0.4619</v>
       </c>
       <c r="G125" t="n">
-        <v>3.2415</v>
+        <v>2.4567</v>
       </c>
       <c r="H125" t="n">
-        <v>6.8267</v>
+        <v>6.9228</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9756</v>
+        <v>0.922</v>
       </c>
       <c r="F126" t="n">
-        <v>1.556</v>
+        <v>0.3978</v>
       </c>
       <c r="G126" t="n">
-        <v>2.6694</v>
+        <v>3.9891</v>
       </c>
       <c r="H126" t="n">
-        <v>7.2649</v>
+        <v>7.3233</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9611</v>
+        <v>0.9655</v>
       </c>
       <c r="F127" t="n">
-        <v>1.6464</v>
+        <v>0.2666</v>
       </c>
       <c r="G127" t="n">
-        <v>3.3133</v>
+        <v>3.0625</v>
       </c>
       <c r="H127" t="n">
-        <v>7.8337</v>
+        <v>8.081899999999999</v>
       </c>
     </row>
     <row r="128">
@@ -4506,20 +4506,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9621</v>
+        <v>0.9135</v>
       </c>
       <c r="F128" t="n">
-        <v>1.5545</v>
+        <v>0.4057</v>
       </c>
       <c r="G128" t="n">
-        <v>3.1482</v>
+        <v>4.1904</v>
       </c>
       <c r="H128" t="n">
-        <v>7.2555</v>
+        <v>7.2751</v>
       </c>
     </row>
     <row r="129">
@@ -4538,20 +4538,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9751</v>
+        <v>0.9145</v>
       </c>
       <c r="F129" t="n">
-        <v>1.5572</v>
+        <v>0.3993</v>
       </c>
       <c r="G129" t="n">
-        <v>2.6851</v>
+        <v>4.1791</v>
       </c>
       <c r="H129" t="n">
-        <v>7.2731</v>
+        <v>7.3141</v>
       </c>
     </row>
     <row r="130">
@@ -4570,20 +4570,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9615</v>
+        <v>0.9205</v>
       </c>
       <c r="F130" t="n">
-        <v>1.5543</v>
+        <v>0.3953</v>
       </c>
       <c r="G130" t="n">
-        <v>3.1615</v>
+        <v>4.0245</v>
       </c>
       <c r="H130" t="n">
-        <v>7.2544</v>
+        <v>7.3386</v>
       </c>
     </row>
     <row r="131">
@@ -4602,20 +4602,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>1.5575</v>
+        <v>0.3954</v>
       </c>
       <c r="G131" t="n">
-        <v>2.6649</v>
+        <v>3.9983</v>
       </c>
       <c r="H131" t="n">
-        <v>7.2748</v>
+        <v>7.338</v>
       </c>
     </row>
     <row r="132">
@@ -4634,20 +4634,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9133</v>
       </c>
       <c r="F132" t="n">
-        <v>1.5551</v>
+        <v>0.3988</v>
       </c>
       <c r="G132" t="n">
-        <v>3.1391</v>
+        <v>4.2135</v>
       </c>
       <c r="H132" t="n">
-        <v>7.2592</v>
+        <v>7.3173</v>
       </c>
     </row>
     <row r="133">
@@ -4666,20 +4666,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9725</v>
+        <v>0.92</v>
       </c>
       <c r="F133" t="n">
-        <v>1.5569</v>
+        <v>0.3969</v>
       </c>
       <c r="G133" t="n">
-        <v>2.7032</v>
+        <v>4.03</v>
       </c>
       <c r="H133" t="n">
-        <v>7.2708</v>
+        <v>7.329</v>
       </c>
     </row>
     <row r="134">
@@ -4698,20 +4698,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9625</v>
+        <v>0.9121</v>
       </c>
       <c r="F134" t="n">
-        <v>1.5594</v>
+        <v>0.4016</v>
       </c>
       <c r="G134" t="n">
-        <v>3.1368</v>
+        <v>4.2099</v>
       </c>
       <c r="H134" t="n">
-        <v>7.2875</v>
+        <v>7.3005</v>
       </c>
     </row>
     <row r="135">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9139</v>
       </c>
       <c r="F135" t="n">
-        <v>1.5582</v>
+        <v>0.4104</v>
       </c>
       <c r="G135" t="n">
-        <v>2.6687</v>
+        <v>4.1756</v>
       </c>
       <c r="H135" t="n">
-        <v>7.2796</v>
+        <v>7.2467</v>
       </c>
     </row>
     <row r="136">
@@ -4762,20 +4762,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9754</v>
+        <v>0.9214</v>
       </c>
       <c r="F136" t="n">
-        <v>1.5595</v>
+        <v>0.3953</v>
       </c>
       <c r="G136" t="n">
-        <v>2.665</v>
+        <v>4.0005</v>
       </c>
       <c r="H136" t="n">
-        <v>7.2883</v>
+        <v>7.3385</v>
       </c>
     </row>
     <row r="137">
@@ -4794,20 +4794,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9702</v>
+        <v>0.9399</v>
       </c>
       <c r="F137" t="n">
-        <v>1.4663</v>
+        <v>0.4603</v>
       </c>
       <c r="G137" t="n">
-        <v>2.7603</v>
+        <v>3.5903</v>
       </c>
       <c r="H137" t="n">
-        <v>6.6531</v>
+        <v>6.9332</v>
       </c>
     </row>
     <row r="138">
@@ -4826,20 +4826,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9727</v>
+        <v>0.9715</v>
       </c>
       <c r="F138" t="n">
-        <v>1.4657</v>
+        <v>0.4976</v>
       </c>
       <c r="G138" t="n">
-        <v>2.6667</v>
+        <v>2.7055</v>
       </c>
       <c r="H138" t="n">
-        <v>6.6494</v>
+        <v>6.6889</v>
       </c>
     </row>
     <row r="139">
@@ -4858,20 +4858,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9712</v>
+        <v>0.9689</v>
       </c>
       <c r="F139" t="n">
-        <v>1.4645</v>
+        <v>0.4506</v>
       </c>
       <c r="G139" t="n">
-        <v>2.7109</v>
+        <v>2.7747</v>
       </c>
       <c r="H139" t="n">
-        <v>6.6404</v>
+        <v>6.9948</v>
       </c>
     </row>
     <row r="140">
@@ -4890,20 +4890,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.98</v>
+        <v>0.979</v>
       </c>
       <c r="F140" t="n">
-        <v>1.4324</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="G140" t="n">
-        <v>2.5053</v>
+        <v>2.5629</v>
       </c>
       <c r="H140" t="n">
-        <v>6.4068</v>
+        <v>6.4296</v>
       </c>
     </row>
     <row r="141">
@@ -4922,20 +4922,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9804</v>
+        <v>0.9785</v>
       </c>
       <c r="F141" t="n">
-        <v>1.4371</v>
+        <v>0.532</v>
       </c>
       <c r="G141" t="n">
-        <v>2.4246</v>
+        <v>2.5408</v>
       </c>
       <c r="H141" t="n">
-        <v>6.4417</v>
+        <v>6.4564</v>
       </c>
     </row>
     <row r="142">
@@ -4954,20 +4954,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9727</v>
+        <v>0.9715</v>
       </c>
       <c r="F142" t="n">
-        <v>1.4657</v>
+        <v>0.4976</v>
       </c>
       <c r="G142" t="n">
-        <v>2.6667</v>
+        <v>2.7055</v>
       </c>
       <c r="H142" t="n">
-        <v>6.6494</v>
+        <v>6.6889</v>
       </c>
     </row>
     <row r="143">
@@ -4986,20 +4986,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9695</v>
+        <v>0.9625</v>
       </c>
       <c r="F143" t="n">
-        <v>1.4771</v>
+        <v>0.442</v>
       </c>
       <c r="G143" t="n">
-        <v>2.8022</v>
+        <v>3.1517</v>
       </c>
       <c r="H143" t="n">
-        <v>6.7299</v>
+        <v>7.0498</v>
       </c>
     </row>
     <row r="144">
@@ -5018,20 +5018,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9695</v>
+        <v>0.9617</v>
       </c>
       <c r="F144" t="n">
-        <v>1.4782</v>
+        <v>0.4403</v>
       </c>
       <c r="G144" t="n">
-        <v>2.7974</v>
+        <v>3.1357</v>
       </c>
       <c r="H144" t="n">
-        <v>6.738</v>
+        <v>7.0606</v>
       </c>
     </row>
     <row r="145">
@@ -5050,20 +5050,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9804</v>
+        <v>0.9785</v>
       </c>
       <c r="F145" t="n">
-        <v>1.4371</v>
+        <v>0.532</v>
       </c>
       <c r="G145" t="n">
-        <v>2.4246</v>
+        <v>2.5408</v>
       </c>
       <c r="H145" t="n">
-        <v>6.4417</v>
+        <v>6.4564</v>
       </c>
     </row>
     <row r="146">
@@ -5082,20 +5082,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.9588</v>
+        <v>0.9663</v>
       </c>
       <c r="F146" t="n">
-        <v>1.654</v>
+        <v>0.2478</v>
       </c>
       <c r="G146" t="n">
-        <v>3.3838</v>
+        <v>3.0353</v>
       </c>
       <c r="H146" t="n">
-        <v>7.8793</v>
+        <v>8.185</v>
       </c>
     </row>
     <row r="147">
@@ -5114,20 +5114,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.9627</v>
+        <v>0.9654</v>
       </c>
       <c r="F147" t="n">
-        <v>1.6614</v>
+        <v>0.2463</v>
       </c>
       <c r="G147" t="n">
-        <v>3.2902</v>
+        <v>3.0482</v>
       </c>
       <c r="H147" t="n">
-        <v>7.9239</v>
+        <v>8.1929</v>
       </c>
     </row>
     <row r="148">
@@ -5150,16 +5150,16 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.9696</v>
+        <v>0.9666</v>
       </c>
       <c r="F148" t="n">
-        <v>1.6575</v>
+        <v>0.2435</v>
       </c>
       <c r="G148" t="n">
-        <v>3.0505</v>
+        <v>3.0391</v>
       </c>
       <c r="H148" t="n">
-        <v>7.9005</v>
+        <v>8.2081</v>
       </c>
     </row>
     <row r="149">
@@ -5178,20 +5178,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.9611</v>
+        <v>0.9741</v>
       </c>
       <c r="F149" t="n">
-        <v>1.6565</v>
+        <v>0.2423</v>
       </c>
       <c r="G149" t="n">
-        <v>3.3181</v>
+        <v>2.9244</v>
       </c>
       <c r="H149" t="n">
-        <v>7.8946</v>
+        <v>8.214499999999999</v>
       </c>
     </row>
     <row r="150">
@@ -5210,20 +5210,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.9587</v>
+        <v>0.9654</v>
       </c>
       <c r="F150" t="n">
-        <v>1.6475</v>
+        <v>0.2656</v>
       </c>
       <c r="G150" t="n">
-        <v>3.3786</v>
+        <v>3.0602</v>
       </c>
       <c r="H150" t="n">
-        <v>7.8401</v>
+        <v>8.087300000000001</v>
       </c>
     </row>
     <row r="151">
@@ -5242,20 +5242,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.9609</v>
+        <v>0.9653</v>
       </c>
       <c r="F151" t="n">
-        <v>1.6468</v>
+        <v>0.2662</v>
       </c>
       <c r="G151" t="n">
-        <v>3.2998</v>
+        <v>3.0668</v>
       </c>
       <c r="H151" t="n">
-        <v>7.8359</v>
+        <v>8.0839</v>
       </c>
     </row>
     <row r="152">
@@ -5278,16 +5278,16 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.9675</v>
+        <v>0.965</v>
       </c>
       <c r="F152" t="n">
-        <v>1.6431</v>
+        <v>0.2582</v>
       </c>
       <c r="G152" t="n">
-        <v>3.0747</v>
+        <v>3.0724</v>
       </c>
       <c r="H152" t="n">
-        <v>7.8138</v>
+        <v>8.1281</v>
       </c>
     </row>
     <row r="153">
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.9673</v>
+        <v>0.9659</v>
       </c>
       <c r="F153" t="n">
-        <v>1.6435</v>
+        <v>0.2621</v>
       </c>
       <c r="G153" t="n">
-        <v>3.0973</v>
+        <v>3.0492</v>
       </c>
       <c r="H153" t="n">
-        <v>7.8162</v>
+        <v>8.1069</v>
       </c>
     </row>
     <row r="154">
@@ -5338,20 +5338,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.9667</v>
+        <v>0.9493</v>
       </c>
       <c r="F154" t="n">
-        <v>1.6467</v>
+        <v>0.2462</v>
       </c>
       <c r="G154" t="n">
-        <v>3.1162</v>
+        <v>3.5688</v>
       </c>
       <c r="H154" t="n">
-        <v>7.8353</v>
+        <v>8.1938</v>
       </c>
     </row>
     <row r="155">
@@ -5370,20 +5370,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.9788</v>
+        <v>0.9778</v>
       </c>
       <c r="F155" t="n">
-        <v>1.436</v>
+        <v>0.4999</v>
       </c>
       <c r="G155" t="n">
-        <v>2.5055</v>
+        <v>2.5606</v>
       </c>
       <c r="H155" t="n">
-        <v>6.4333</v>
+        <v>6.6742</v>
       </c>
     </row>
     <row r="156">
@@ -5402,20 +5402,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.9812</v>
+        <v>0.9777</v>
       </c>
       <c r="F156" t="n">
-        <v>1.4398</v>
+        <v>0.4807</v>
       </c>
       <c r="G156" t="n">
-        <v>2.4181</v>
+        <v>2.587</v>
       </c>
       <c r="H156" t="n">
-        <v>6.4617</v>
+        <v>6.8009</v>
       </c>
     </row>
     <row r="157">
@@ -5434,20 +5434,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="F157" t="n">
-        <v>1.4493</v>
+        <v>0.4638</v>
       </c>
       <c r="G157" t="n">
-        <v>2.583</v>
+        <v>3.0435</v>
       </c>
       <c r="H157" t="n">
-        <v>6.5311</v>
+        <v>6.9108</v>
       </c>
     </row>
     <row r="158">
@@ -5466,20 +5466,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.982</v>
+        <v>0.98</v>
       </c>
       <c r="F158" t="n">
-        <v>1.3309</v>
+        <v>0.6158</v>
       </c>
       <c r="G158" t="n">
-        <v>2.205</v>
+        <v>2.2876</v>
       </c>
       <c r="H158" t="n">
-        <v>5.6051</v>
+        <v>5.8498</v>
       </c>
     </row>
     <row r="159">
@@ -5498,20 +5498,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.967</v>
+        <v>0.9201</v>
       </c>
       <c r="F159" t="n">
-        <v>1.5575</v>
+        <v>0.386</v>
       </c>
       <c r="G159" t="n">
-        <v>2.9495</v>
+        <v>4.0955</v>
       </c>
       <c r="H159" t="n">
-        <v>7.275</v>
+        <v>7.3951</v>
       </c>
     </row>
     <row r="160">
@@ -5534,16 +5534,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.9614</v>
+        <v>0.9571</v>
       </c>
       <c r="F160" t="n">
-        <v>1.696</v>
+        <v>0.2137</v>
       </c>
       <c r="G160" t="n">
-        <v>3.4271</v>
+        <v>3.4867</v>
       </c>
       <c r="H160" t="n">
-        <v>8.1286</v>
+        <v>8.3682</v>
       </c>
     </row>
     <row r="161">
@@ -5562,20 +5562,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.9537</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="F161" t="n">
-        <v>1.6973</v>
+        <v>0.2053</v>
       </c>
       <c r="G161" t="n">
-        <v>3.7082</v>
+        <v>4.0032</v>
       </c>
       <c r="H161" t="n">
-        <v>8.135899999999999</v>
+        <v>8.413</v>
       </c>
     </row>
     <row r="162">
@@ -5594,20 +5594,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9692</v>
+        <v>0.9181</v>
       </c>
       <c r="F162" t="n">
-        <v>1.559</v>
+        <v>0.375</v>
       </c>
       <c r="G162" t="n">
-        <v>2.8768</v>
+        <v>4.1398</v>
       </c>
       <c r="H162" t="n">
-        <v>7.2846</v>
+        <v>7.4607</v>
       </c>
     </row>
     <row r="163">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9691</v>
+        <v>0.9597</v>
       </c>
       <c r="F163" t="n">
-        <v>1.4812</v>
+        <v>0.4676</v>
       </c>
       <c r="G163" t="n">
-        <v>2.7986</v>
+        <v>3.1544</v>
       </c>
       <c r="H163" t="n">
-        <v>6.7591</v>
+        <v>6.8863</v>
       </c>
     </row>
     <row r="164">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9802</v>
       </c>
       <c r="F164" t="n">
-        <v>1.4319</v>
+        <v>0.5361</v>
       </c>
       <c r="G164" t="n">
-        <v>2.5516</v>
+        <v>2.501</v>
       </c>
       <c r="H164" t="n">
-        <v>6.403</v>
+        <v>6.4276</v>
       </c>
     </row>
     <row r="165">
@@ -5690,20 +5690,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9513</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F165" t="n">
-        <v>1.4909</v>
+        <v>0.4619</v>
       </c>
       <c r="G165" t="n">
-        <v>3.2415</v>
+        <v>2.4567</v>
       </c>
       <c r="H165" t="n">
-        <v>6.8267</v>
+        <v>6.9228</v>
       </c>
     </row>
     <row r="166">
@@ -5722,20 +5722,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.9499</v>
       </c>
       <c r="F166" t="n">
-        <v>1.5271</v>
+        <v>0.4222</v>
       </c>
       <c r="G166" t="n">
-        <v>4.1177</v>
+        <v>3.1476</v>
       </c>
       <c r="H166" t="n">
-        <v>7.074</v>
+        <v>7.1735</v>
       </c>
     </row>
     <row r="167">
@@ -5754,20 +5754,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9704</v>
+        <v>0.9484</v>
       </c>
       <c r="F167" t="n">
-        <v>1.4545</v>
+        <v>0.4731</v>
       </c>
       <c r="G167" t="n">
-        <v>2.7079</v>
+        <v>3.3992</v>
       </c>
       <c r="H167" t="n">
-        <v>6.5684</v>
+        <v>6.8505</v>
       </c>
     </row>
     <row r="168">
@@ -5786,20 +5786,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9738</v>
+        <v>0.9635</v>
       </c>
       <c r="F168" t="n">
-        <v>1.4844</v>
+        <v>0.4671</v>
       </c>
       <c r="G168" t="n">
-        <v>2.9207</v>
+        <v>3.2357</v>
       </c>
       <c r="H168" t="n">
-        <v>6.7816</v>
+        <v>6.8893</v>
       </c>
     </row>
     <row r="169">
@@ -5818,20 +5818,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9835</v>
+        <v>0.9829</v>
       </c>
       <c r="F169" t="n">
-        <v>1.3722</v>
+        <v>0.587</v>
       </c>
       <c r="G169" t="n">
-        <v>2.2512</v>
+        <v>2.288</v>
       </c>
       <c r="H169" t="n">
-        <v>5.9447</v>
+        <v>6.0651</v>
       </c>
     </row>
     <row r="170">
@@ -5850,20 +5850,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9691</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F170" t="n">
-        <v>1.5478</v>
+        <v>0.4292</v>
       </c>
       <c r="G170" t="n">
-        <v>3.3713</v>
+        <v>2.9083</v>
       </c>
       <c r="H170" t="n">
-        <v>7.2117</v>
+        <v>7.1302</v>
       </c>
     </row>
     <row r="171">
@@ -5882,20 +5882,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9804</v>
+        <v>0.9706</v>
       </c>
       <c r="F171" t="n">
-        <v>1.4734</v>
+        <v>0.5152</v>
       </c>
       <c r="G171" t="n">
-        <v>2.6953</v>
+        <v>3.1359</v>
       </c>
       <c r="H171" t="n">
-        <v>6.7041</v>
+        <v>6.5712</v>
       </c>
     </row>
     <row r="172">
@@ -5914,20 +5914,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9738</v>
+        <v>0.9369</v>
       </c>
       <c r="F172" t="n">
-        <v>1.5204</v>
+        <v>0.458</v>
       </c>
       <c r="G172" t="n">
-        <v>2.7303</v>
+        <v>3.7366</v>
       </c>
       <c r="H172" t="n">
-        <v>7.029</v>
+        <v>6.948</v>
       </c>
     </row>
   </sheetData>
